--- a/artfynd/A 47917-2023 artfynd.xlsx
+++ b/artfynd/A 47917-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117711812</v>
+        <v>117711386</v>
       </c>
       <c r="B2" t="n">
-        <v>78480</v>
+        <v>78514</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465285</v>
+        <v>465484</v>
       </c>
       <c r="R2" t="n">
-        <v>6823267</v>
+        <v>6822737</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117711686</v>
+        <v>117711812</v>
       </c>
       <c r="B3" t="n">
-        <v>78216</v>
+        <v>78480</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465453</v>
+        <v>465285</v>
       </c>
       <c r="R3" t="n">
-        <v>6822624</v>
+        <v>6823267</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117711557</v>
+        <v>117711686</v>
       </c>
       <c r="B4" t="n">
-        <v>79590</v>
+        <v>78216</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,41 +891,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465117</v>
+        <v>465453</v>
       </c>
       <c r="R4" t="n">
-        <v>6823218</v>
+        <v>6822624</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,18 +957,12 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På asp</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -990,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117711386</v>
+        <v>117711557</v>
       </c>
       <c r="B5" t="n">
-        <v>78514</v>
+        <v>79590</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,38 +993,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465484</v>
+        <v>465117</v>
       </c>
       <c r="R5" t="n">
-        <v>6822737</v>
+        <v>6823218</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,12 +1062,18 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På asp</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1092,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117711400</v>
+        <v>117711630</v>
       </c>
       <c r="B6" t="n">
-        <v>78514</v>
+        <v>78217</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1108,21 +1108,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465326</v>
+        <v>465362</v>
       </c>
       <c r="R6" t="n">
-        <v>6823285</v>
+        <v>6822857</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117711988</v>
+        <v>117711655</v>
       </c>
       <c r="B7" t="n">
-        <v>78125</v>
+        <v>78217</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1210,21 +1210,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1234,10 +1234,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465229</v>
+        <v>465092</v>
       </c>
       <c r="R7" t="n">
-        <v>6823280</v>
+        <v>6823190</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117711685</v>
+        <v>117711400</v>
       </c>
       <c r="B8" t="n">
-        <v>78216</v>
+        <v>78514</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1312,41 +1312,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465797</v>
+        <v>465326</v>
       </c>
       <c r="R8" t="n">
-        <v>6822438</v>
+        <v>6823285</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1380,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1406,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117711747</v>
+        <v>117711988</v>
       </c>
       <c r="B9" t="n">
-        <v>78480</v>
+        <v>78125</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1422,21 +1414,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1446,10 +1438,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465604</v>
+        <v>465229</v>
       </c>
       <c r="R9" t="n">
-        <v>6822515</v>
+        <v>6823280</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1508,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117711444</v>
+        <v>117711685</v>
       </c>
       <c r="B10" t="n">
-        <v>79098</v>
+        <v>78216</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1524,34 +1516,41 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465036</v>
+        <v>465797</v>
       </c>
       <c r="R10" t="n">
-        <v>6823260</v>
+        <v>6822438</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,6 +1591,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1610,10 +1610,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117711630</v>
+        <v>117711747</v>
       </c>
       <c r="B11" t="n">
-        <v>78217</v>
+        <v>78480</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1626,21 +1626,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1650,10 +1650,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465362</v>
+        <v>465604</v>
       </c>
       <c r="R11" t="n">
-        <v>6822857</v>
+        <v>6822515</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1712,10 +1712,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117711655</v>
+        <v>117711444</v>
       </c>
       <c r="B12" t="n">
-        <v>78217</v>
+        <v>79098</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1728,21 +1728,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465092</v>
+        <v>465036</v>
       </c>
       <c r="R12" t="n">
-        <v>6823190</v>
+        <v>6823260</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2651,10 +2651,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117711597</v>
+        <v>117711426</v>
       </c>
       <c r="B21" t="n">
-        <v>57287</v>
+        <v>79098</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2667,42 +2667,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>465248</v>
+        <v>465566</v>
       </c>
       <c r="R21" t="n">
-        <v>6823304</v>
+        <v>6822693</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2735,11 +2727,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-06-10</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2766,10 +2753,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117711426</v>
+        <v>117711597</v>
       </c>
       <c r="B22" t="n">
-        <v>79098</v>
+        <v>57287</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2782,34 +2769,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>465566</v>
+        <v>465248</v>
       </c>
       <c r="R22" t="n">
-        <v>6822693</v>
+        <v>6823304</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2842,6 +2837,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3378,10 +3378,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117711987</v>
+        <v>117711810</v>
       </c>
       <c r="B28" t="n">
-        <v>78125</v>
+        <v>78480</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3394,21 +3394,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3418,10 +3418,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>465232</v>
+        <v>465284</v>
       </c>
       <c r="R28" t="n">
-        <v>6823416</v>
+        <v>6823283</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3582,10 +3582,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117711810</v>
+        <v>117711987</v>
       </c>
       <c r="B30" t="n">
-        <v>78480</v>
+        <v>78125</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3598,21 +3598,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3622,10 +3622,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>465284</v>
+        <v>465232</v>
       </c>
       <c r="R30" t="n">
-        <v>6823283</v>
+        <v>6823416</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -7050,10 +7050,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>117711693</v>
+        <v>117711417</v>
       </c>
       <c r="B64" t="n">
-        <v>78216</v>
+        <v>79098</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7066,21 +7066,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7090,10 +7090,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>465629</v>
+        <v>465453</v>
       </c>
       <c r="R64" t="n">
-        <v>6822491</v>
+        <v>6822624</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7152,10 +7152,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>117711434</v>
+        <v>117711629</v>
       </c>
       <c r="B65" t="n">
-        <v>79098</v>
+        <v>78217</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7168,21 +7168,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7192,10 +7192,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>465812</v>
+        <v>465398</v>
       </c>
       <c r="R65" t="n">
-        <v>6822424</v>
+        <v>6822827</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7254,10 +7254,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>117711417</v>
+        <v>117711693</v>
       </c>
       <c r="B66" t="n">
-        <v>79098</v>
+        <v>78216</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7270,21 +7270,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7294,10 +7294,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>465453</v>
+        <v>465629</v>
       </c>
       <c r="R66" t="n">
-        <v>6822624</v>
+        <v>6822491</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7356,10 +7356,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>117711629</v>
+        <v>117711434</v>
       </c>
       <c r="B67" t="n">
-        <v>78217</v>
+        <v>79098</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7372,21 +7372,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7396,10 +7396,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>465398</v>
+        <v>465812</v>
       </c>
       <c r="R67" t="n">
-        <v>6822827</v>
+        <v>6822424</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7662,10 +7662,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>117711637</v>
+        <v>117711429</v>
       </c>
       <c r="B70" t="n">
-        <v>78217</v>
+        <v>79098</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7678,21 +7678,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7702,10 +7702,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>465540</v>
+        <v>465655</v>
       </c>
       <c r="R70" t="n">
-        <v>6822684</v>
+        <v>6822559</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7764,10 +7764,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>117711635</v>
+        <v>117711433</v>
       </c>
       <c r="B71" t="n">
-        <v>78217</v>
+        <v>79098</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7780,21 +7780,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7804,10 +7804,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>465508</v>
+        <v>465750</v>
       </c>
       <c r="R71" t="n">
-        <v>6822811</v>
+        <v>6822471</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7866,7 +7866,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>117711429</v>
+        <v>117711437</v>
       </c>
       <c r="B72" t="n">
         <v>79098</v>
@@ -7906,10 +7906,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>465655</v>
+        <v>465604</v>
       </c>
       <c r="R72" t="n">
-        <v>6822559</v>
+        <v>6822495</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7968,10 +7968,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>117711433</v>
+        <v>117711733</v>
       </c>
       <c r="B73" t="n">
-        <v>79098</v>
+        <v>90517</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7984,21 +7984,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8008,10 +8008,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>465750</v>
+        <v>465286</v>
       </c>
       <c r="R73" t="n">
-        <v>6822471</v>
+        <v>6823284</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8070,10 +8070,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>117711437</v>
+        <v>117711637</v>
       </c>
       <c r="B74" t="n">
-        <v>79098</v>
+        <v>78217</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8086,21 +8086,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8110,10 +8110,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>465604</v>
+        <v>465540</v>
       </c>
       <c r="R74" t="n">
-        <v>6822495</v>
+        <v>6822684</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8172,10 +8172,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>117711733</v>
+        <v>117711635</v>
       </c>
       <c r="B75" t="n">
-        <v>90517</v>
+        <v>78217</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8188,21 +8188,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5432</v>
+        <v>228912</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8212,10 +8212,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>465286</v>
+        <v>465508</v>
       </c>
       <c r="R75" t="n">
-        <v>6823284</v>
+        <v>6822811</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10257,10 +10257,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>117711606</v>
+        <v>117711631</v>
       </c>
       <c r="B95" t="n">
-        <v>96797</v>
+        <v>78217</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10269,25 +10269,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>221941</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10297,10 +10297,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>465576</v>
+        <v>465358</v>
       </c>
       <c r="R95" t="n">
-        <v>6822530</v>
+        <v>6822917</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10359,10 +10359,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>117711631</v>
+        <v>117711606</v>
       </c>
       <c r="B96" t="n">
-        <v>78217</v>
+        <v>96797</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10371,25 +10371,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228912</v>
+        <v>221941</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10399,10 +10399,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>465358</v>
+        <v>465576</v>
       </c>
       <c r="R96" t="n">
-        <v>6822917</v>
+        <v>6822530</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10563,10 +10563,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>117711441</v>
+        <v>117711703</v>
       </c>
       <c r="B98" t="n">
-        <v>79098</v>
+        <v>78216</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10579,21 +10579,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10603,10 +10603,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>465167</v>
+        <v>465145</v>
       </c>
       <c r="R98" t="n">
-        <v>6823048</v>
+        <v>6823279</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10665,10 +10665,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>117711545</v>
+        <v>117711692</v>
       </c>
       <c r="B99" t="n">
-        <v>56499</v>
+        <v>78216</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10677,46 +10677,38 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>465578</v>
+        <v>465656</v>
       </c>
       <c r="R99" t="n">
-        <v>6822532</v>
+        <v>6822514</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10775,10 +10767,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>117711703</v>
+        <v>117711441</v>
       </c>
       <c r="B100" t="n">
-        <v>78216</v>
+        <v>79098</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10791,21 +10783,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10815,10 +10807,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>465145</v>
+        <v>465167</v>
       </c>
       <c r="R100" t="n">
-        <v>6823279</v>
+        <v>6823048</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10877,10 +10869,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>117711692</v>
+        <v>117711545</v>
       </c>
       <c r="B101" t="n">
-        <v>78216</v>
+        <v>56499</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10889,38 +10881,46 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>465656</v>
+        <v>465578</v>
       </c>
       <c r="R101" t="n">
-        <v>6822514</v>
+        <v>6822532</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10979,10 +10979,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>117711790</v>
+        <v>117711399</v>
       </c>
       <c r="B102" t="n">
-        <v>78480</v>
+        <v>78514</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10995,21 +10995,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11019,10 +11019,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>465200</v>
+        <v>465258</v>
       </c>
       <c r="R102" t="n">
-        <v>6823139</v>
+        <v>6823270</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11081,10 +11081,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>117711799</v>
+        <v>117711391</v>
       </c>
       <c r="B103" t="n">
-        <v>78480</v>
+        <v>78514</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11097,21 +11097,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11121,10 +11121,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>465272</v>
+        <v>465658</v>
       </c>
       <c r="R103" t="n">
-        <v>6823356</v>
+        <v>6822562</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11183,7 +11183,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>117711793</v>
+        <v>117711790</v>
       </c>
       <c r="B104" t="n">
         <v>78480</v>
@@ -11223,10 +11223,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>465118</v>
+        <v>465200</v>
       </c>
       <c r="R104" t="n">
-        <v>6823227</v>
+        <v>6823139</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11285,10 +11285,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>117711648</v>
+        <v>117711799</v>
       </c>
       <c r="B105" t="n">
-        <v>78217</v>
+        <v>78480</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11301,21 +11301,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11325,10 +11325,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>465691</v>
+        <v>465272</v>
       </c>
       <c r="R105" t="n">
-        <v>6822493</v>
+        <v>6823356</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11387,10 +11387,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>117711399</v>
+        <v>117711793</v>
       </c>
       <c r="B106" t="n">
-        <v>78514</v>
+        <v>78480</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11403,21 +11403,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11427,10 +11427,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>465258</v>
+        <v>465118</v>
       </c>
       <c r="R106" t="n">
-        <v>6823270</v>
+        <v>6823227</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11489,10 +11489,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>117711391</v>
+        <v>117711648</v>
       </c>
       <c r="B107" t="n">
-        <v>78514</v>
+        <v>78217</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11505,21 +11505,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11529,10 +11529,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>465658</v>
+        <v>465691</v>
       </c>
       <c r="R107" t="n">
-        <v>6822562</v>
+        <v>6822493</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12012,10 +12012,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>117711628</v>
+        <v>117711530</v>
       </c>
       <c r="B112" t="n">
-        <v>78217</v>
+        <v>90499</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12028,21 +12028,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12052,10 +12052,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>465491</v>
+        <v>465283</v>
       </c>
       <c r="R112" t="n">
-        <v>6822739</v>
+        <v>6823280</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12114,10 +12114,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>117711530</v>
+        <v>117711743</v>
       </c>
       <c r="B113" t="n">
-        <v>90499</v>
+        <v>78480</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12130,21 +12130,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12154,10 +12154,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>465283</v>
+        <v>465421</v>
       </c>
       <c r="R113" t="n">
-        <v>6823280</v>
+        <v>6822897</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12216,10 +12216,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>117711743</v>
+        <v>117711688</v>
       </c>
       <c r="B114" t="n">
-        <v>78480</v>
+        <v>78216</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12232,21 +12232,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12256,10 +12256,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>465421</v>
+        <v>465494</v>
       </c>
       <c r="R114" t="n">
-        <v>6822897</v>
+        <v>6822741</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12318,10 +12318,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>117711688</v>
+        <v>117711420</v>
       </c>
       <c r="B115" t="n">
-        <v>78216</v>
+        <v>79098</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12334,21 +12334,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12358,10 +12358,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>465494</v>
+        <v>465373</v>
       </c>
       <c r="R115" t="n">
-        <v>6822741</v>
+        <v>6822775</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12420,7 +12420,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>117711420</v>
+        <v>117711432</v>
       </c>
       <c r="B116" t="n">
         <v>79098</v>
@@ -12460,10 +12460,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>465373</v>
+        <v>465744</v>
       </c>
       <c r="R116" t="n">
-        <v>6822775</v>
+        <v>6822471</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12522,7 +12522,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>117711432</v>
+        <v>117711455</v>
       </c>
       <c r="B117" t="n">
         <v>79098</v>
@@ -12562,10 +12562,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>465744</v>
+        <v>465215</v>
       </c>
       <c r="R117" t="n">
-        <v>6822471</v>
+        <v>6823375</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12624,10 +12624,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>117711455</v>
+        <v>117712002</v>
       </c>
       <c r="B118" t="n">
-        <v>79098</v>
+        <v>91772</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12636,25 +12636,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12664,10 +12664,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>465215</v>
+        <v>465293</v>
       </c>
       <c r="R118" t="n">
-        <v>6823375</v>
+        <v>6823387</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12726,10 +12726,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>117711535</v>
+        <v>117711728</v>
       </c>
       <c r="B119" t="n">
-        <v>57287</v>
+        <v>90648</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12738,46 +12738,38 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100109</v>
+        <v>1503</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>465168</v>
+        <v>465382</v>
       </c>
       <c r="R119" t="n">
-        <v>6823294</v>
+        <v>6822811</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12810,11 +12802,6 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2024-06-10</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Bo, troligen använt 2023</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12841,10 +12828,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>117712002</v>
+        <v>117711628</v>
       </c>
       <c r="B120" t="n">
-        <v>91772</v>
+        <v>78217</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12853,25 +12840,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12881,10 +12868,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>465293</v>
+        <v>465491</v>
       </c>
       <c r="R120" t="n">
-        <v>6823387</v>
+        <v>6822739</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12943,10 +12930,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>117711728</v>
+        <v>117711535</v>
       </c>
       <c r="B121" t="n">
-        <v>90648</v>
+        <v>57287</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -12955,38 +12942,46 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1503</v>
+        <v>100109</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>465382</v>
+        <v>465168</v>
       </c>
       <c r="R121" t="n">
-        <v>6822811</v>
+        <v>6823294</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13019,6 +13014,11 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Bo, troligen använt 2023</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13045,10 +13045,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>117711450</v>
+        <v>117711398</v>
       </c>
       <c r="B122" t="n">
-        <v>79098</v>
+        <v>78514</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13061,21 +13061,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13085,10 +13085,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>465326</v>
+        <v>465275</v>
       </c>
       <c r="R122" t="n">
-        <v>6823374</v>
+        <v>6823367</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13555,10 +13555,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>117711398</v>
+        <v>117711443</v>
       </c>
       <c r="B127" t="n">
-        <v>78514</v>
+        <v>79098</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13571,21 +13571,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13595,10 +13595,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>465275</v>
+        <v>465047</v>
       </c>
       <c r="R127" t="n">
-        <v>6823367</v>
+        <v>6823271</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13657,7 +13657,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>117711443</v>
+        <v>117711451</v>
       </c>
       <c r="B128" t="n">
         <v>79098</v>
@@ -13697,10 +13697,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>465047</v>
+        <v>465293</v>
       </c>
       <c r="R128" t="n">
-        <v>6823271</v>
+        <v>6823407</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13759,7 +13759,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>117711451</v>
+        <v>117711450</v>
       </c>
       <c r="B129" t="n">
         <v>79098</v>
@@ -13799,10 +13799,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>465293</v>
+        <v>465326</v>
       </c>
       <c r="R129" t="n">
-        <v>6823407</v>
+        <v>6823374</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>

--- a/artfynd/A 47917-2023 artfynd.xlsx
+++ b/artfynd/A 47917-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117711386</v>
+        <v>117711728</v>
       </c>
       <c r="B2" t="n">
-        <v>78514</v>
+        <v>90648</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>185</v>
+        <v>1503</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465484</v>
+        <v>465382</v>
       </c>
       <c r="R2" t="n">
-        <v>6822737</v>
+        <v>6822811</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117711812</v>
+        <v>117711795</v>
       </c>
       <c r="B3" t="n">
         <v>78480</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465285</v>
+        <v>465163</v>
       </c>
       <c r="R3" t="n">
-        <v>6823267</v>
+        <v>6823288</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117711686</v>
+        <v>117711812</v>
       </c>
       <c r="B4" t="n">
-        <v>78216</v>
+        <v>78480</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465453</v>
+        <v>465285</v>
       </c>
       <c r="R4" t="n">
-        <v>6822624</v>
+        <v>6823267</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117711557</v>
+        <v>117711451</v>
       </c>
       <c r="B5" t="n">
-        <v>79590</v>
+        <v>79098</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,41 +993,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465117</v>
+        <v>465293</v>
       </c>
       <c r="R5" t="n">
-        <v>6823218</v>
+        <v>6823407</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,18 +1059,12 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På asp</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1092,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117711630</v>
+        <v>117711455</v>
       </c>
       <c r="B6" t="n">
-        <v>78217</v>
+        <v>79098</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1108,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465362</v>
+        <v>465215</v>
       </c>
       <c r="R6" t="n">
-        <v>6822857</v>
+        <v>6823375</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117711655</v>
+        <v>117711425</v>
       </c>
       <c r="B7" t="n">
-        <v>78217</v>
+        <v>79098</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1210,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1234,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465092</v>
+        <v>465537</v>
       </c>
       <c r="R7" t="n">
-        <v>6823190</v>
+        <v>6822683</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117711400</v>
+        <v>117711449</v>
       </c>
       <c r="B8" t="n">
-        <v>78514</v>
+        <v>79098</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1312,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465326</v>
+        <v>465140</v>
       </c>
       <c r="R8" t="n">
-        <v>6823285</v>
+        <v>6823344</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117711988</v>
+        <v>117711686</v>
       </c>
       <c r="B9" t="n">
-        <v>78125</v>
+        <v>78216</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1414,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1438,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465229</v>
+        <v>465453</v>
       </c>
       <c r="R9" t="n">
-        <v>6823280</v>
+        <v>6822624</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117711685</v>
+        <v>117711419</v>
       </c>
       <c r="B10" t="n">
-        <v>78216</v>
+        <v>79098</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1516,41 +1507,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465797</v>
+        <v>465488</v>
       </c>
       <c r="R10" t="n">
-        <v>6822438</v>
+        <v>6822741</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1591,7 +1575,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1610,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117711747</v>
+        <v>117712009</v>
       </c>
       <c r="B11" t="n">
-        <v>78480</v>
+        <v>77864</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1626,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1650,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465604</v>
+        <v>465568</v>
       </c>
       <c r="R11" t="n">
-        <v>6822515</v>
+        <v>6822697</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1712,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117711444</v>
+        <v>117711545</v>
       </c>
       <c r="B12" t="n">
-        <v>79098</v>
+        <v>56499</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1724,38 +1707,46 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465036</v>
+        <v>465578</v>
       </c>
       <c r="R12" t="n">
-        <v>6823260</v>
+        <v>6822532</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1814,10 +1805,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117711544</v>
+        <v>117711644</v>
       </c>
       <c r="B13" t="n">
-        <v>56499</v>
+        <v>78217</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1826,46 +1817,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>465222</v>
+        <v>465798</v>
       </c>
       <c r="R13" t="n">
-        <v>6823415</v>
+        <v>6822436</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1924,10 +1907,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117711388</v>
+        <v>117711626</v>
       </c>
       <c r="B14" t="n">
-        <v>78514</v>
+        <v>78217</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1940,21 +1923,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1964,10 +1947,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465465</v>
+        <v>465453</v>
       </c>
       <c r="R14" t="n">
-        <v>6822863</v>
+        <v>6822624</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2026,10 +2009,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117711813</v>
+        <v>117711627</v>
       </c>
       <c r="B15" t="n">
-        <v>78480</v>
+        <v>78217</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2042,21 +2025,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2066,10 +2049,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465306</v>
+        <v>465477</v>
       </c>
       <c r="R15" t="n">
-        <v>6823279</v>
+        <v>6822612</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2128,10 +2111,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117711419</v>
+        <v>117711805</v>
       </c>
       <c r="B16" t="n">
-        <v>79098</v>
+        <v>78480</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2144,21 +2127,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2168,10 +2151,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>465488</v>
+        <v>465244</v>
       </c>
       <c r="R16" t="n">
-        <v>6822741</v>
+        <v>6823294</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2230,10 +2213,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117711425</v>
+        <v>117711794</v>
       </c>
       <c r="B17" t="n">
-        <v>79098</v>
+        <v>78480</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2246,21 +2229,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2270,10 +2253,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>465537</v>
+        <v>465131</v>
       </c>
       <c r="R17" t="n">
-        <v>6822683</v>
+        <v>6823271</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2332,10 +2315,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117711592</v>
+        <v>117711799</v>
       </c>
       <c r="B18" t="n">
-        <v>57287</v>
+        <v>78480</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2348,42 +2331,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>465242</v>
+        <v>465272</v>
       </c>
       <c r="R18" t="n">
-        <v>6822897</v>
+        <v>6823356</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2416,11 +2391,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-06-10</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2447,10 +2417,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117711644</v>
+        <v>117711433</v>
       </c>
       <c r="B19" t="n">
-        <v>78217</v>
+        <v>79098</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2463,21 +2433,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2487,10 +2457,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>465798</v>
+        <v>465750</v>
       </c>
       <c r="R19" t="n">
-        <v>6822436</v>
+        <v>6822471</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2549,10 +2519,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117711423</v>
+        <v>117711655</v>
       </c>
       <c r="B20" t="n">
-        <v>79098</v>
+        <v>78217</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2565,21 +2535,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2589,10 +2559,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>465448</v>
+        <v>465092</v>
       </c>
       <c r="R20" t="n">
-        <v>6822872</v>
+        <v>6823190</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2651,10 +2621,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117711426</v>
+        <v>117711629</v>
       </c>
       <c r="B21" t="n">
-        <v>79098</v>
+        <v>78217</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2667,21 +2637,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2691,10 +2661,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>465566</v>
+        <v>465398</v>
       </c>
       <c r="R21" t="n">
-        <v>6822693</v>
+        <v>6822827</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2753,10 +2723,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117711597</v>
+        <v>117711633</v>
       </c>
       <c r="B22" t="n">
-        <v>57287</v>
+        <v>78217</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2769,42 +2739,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>465248</v>
+        <v>465425</v>
       </c>
       <c r="R22" t="n">
-        <v>6823304</v>
+        <v>6822873</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2837,11 +2799,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-06-10</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2868,10 +2825,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117711649</v>
+        <v>117711390</v>
       </c>
       <c r="B23" t="n">
-        <v>78217</v>
+        <v>78514</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2884,21 +2841,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2908,10 +2865,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>465644</v>
+        <v>465508</v>
       </c>
       <c r="R23" t="n">
-        <v>6822519</v>
+        <v>6822804</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2970,7 +2927,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117711387</v>
+        <v>117711391</v>
       </c>
       <c r="B24" t="n">
         <v>78514</v>
@@ -3010,10 +2967,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465419</v>
+        <v>465658</v>
       </c>
       <c r="R24" t="n">
-        <v>6822910</v>
+        <v>6822562</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3072,10 +3029,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117711791</v>
+        <v>117711682</v>
       </c>
       <c r="B25" t="n">
-        <v>78480</v>
+        <v>80437</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3088,21 +3045,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3112,10 +3069,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>465146</v>
+        <v>465659</v>
       </c>
       <c r="R25" t="n">
-        <v>6823190</v>
+        <v>6822514</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3174,10 +3131,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117711457</v>
+        <v>117711747</v>
       </c>
       <c r="B26" t="n">
-        <v>79098</v>
+        <v>78480</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3190,21 +3147,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3214,10 +3171,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>465273</v>
+        <v>465604</v>
       </c>
       <c r="R26" t="n">
-        <v>6823001</v>
+        <v>6822515</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3276,10 +3233,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117711683</v>
+        <v>117711447</v>
       </c>
       <c r="B27" t="n">
-        <v>80437</v>
+        <v>79098</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3292,21 +3249,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3316,10 +3273,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>465335</v>
+        <v>465137</v>
       </c>
       <c r="R27" t="n">
-        <v>6823378</v>
+        <v>6823348</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3378,10 +3335,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117711810</v>
+        <v>117711417</v>
       </c>
       <c r="B28" t="n">
-        <v>78480</v>
+        <v>79098</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3394,21 +3351,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3418,10 +3375,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>465284</v>
+        <v>465453</v>
       </c>
       <c r="R28" t="n">
-        <v>6823283</v>
+        <v>6822624</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3480,10 +3437,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117711795</v>
+        <v>117711450</v>
       </c>
       <c r="B29" t="n">
-        <v>78480</v>
+        <v>79098</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3496,21 +3453,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3520,10 +3477,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>465163</v>
+        <v>465326</v>
       </c>
       <c r="R29" t="n">
-        <v>6823288</v>
+        <v>6823374</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3582,10 +3539,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117711987</v>
+        <v>117711706</v>
       </c>
       <c r="B30" t="n">
-        <v>78125</v>
+        <v>78216</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3598,21 +3555,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3622,10 +3579,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>465232</v>
+        <v>465257</v>
       </c>
       <c r="R30" t="n">
-        <v>6823416</v>
+        <v>6823270</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3684,10 +3641,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117711634</v>
+        <v>117711684</v>
       </c>
       <c r="B31" t="n">
-        <v>78217</v>
+        <v>79521</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3696,25 +3653,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>229497</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3724,10 +3681,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>465448</v>
+        <v>465128</v>
       </c>
       <c r="R31" t="n">
-        <v>6822872</v>
+        <v>6823219</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3786,10 +3743,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117711633</v>
+        <v>117711452</v>
       </c>
       <c r="B32" t="n">
-        <v>78217</v>
+        <v>79098</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3802,21 +3759,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3826,10 +3783,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>465425</v>
+        <v>465263</v>
       </c>
       <c r="R32" t="n">
-        <v>6822873</v>
+        <v>6823399</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3888,10 +3845,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117711636</v>
+        <v>117711744</v>
       </c>
       <c r="B33" t="n">
-        <v>78217</v>
+        <v>78480</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3904,21 +3861,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3928,10 +3885,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>465528</v>
+        <v>465439</v>
       </c>
       <c r="R33" t="n">
-        <v>6822701</v>
+        <v>6822881</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3990,10 +3947,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117711449</v>
+        <v>117711703</v>
       </c>
       <c r="B34" t="n">
-        <v>79098</v>
+        <v>78216</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4006,21 +3963,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4030,10 +3987,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>465140</v>
+        <v>465145</v>
       </c>
       <c r="R34" t="n">
-        <v>6823344</v>
+        <v>6823279</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4092,10 +4049,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117711701</v>
+        <v>117711420</v>
       </c>
       <c r="B35" t="n">
-        <v>78216</v>
+        <v>79098</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4108,21 +4065,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4132,10 +4089,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>465157</v>
+        <v>465373</v>
       </c>
       <c r="R35" t="n">
-        <v>6823202</v>
+        <v>6822775</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4194,10 +4151,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117711446</v>
+        <v>117711535</v>
       </c>
       <c r="B36" t="n">
-        <v>79098</v>
+        <v>57287</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4210,34 +4167,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>465106</v>
+        <v>465168</v>
       </c>
       <c r="R36" t="n">
-        <v>6823211</v>
+        <v>6823294</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4270,6 +4235,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Bo, troligen använt 2023</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4296,10 +4266,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117711445</v>
+        <v>117711628</v>
       </c>
       <c r="B37" t="n">
-        <v>79098</v>
+        <v>78217</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4312,21 +4282,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4336,10 +4306,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>465092</v>
+        <v>465491</v>
       </c>
       <c r="R37" t="n">
-        <v>6823189</v>
+        <v>6822739</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4398,10 +4368,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117711522</v>
+        <v>117711816</v>
       </c>
       <c r="B38" t="n">
-        <v>79069</v>
+        <v>78480</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4414,21 +4384,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4438,10 +4408,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>465398</v>
+        <v>465243</v>
       </c>
       <c r="R38" t="n">
-        <v>6822828</v>
+        <v>6822961</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4500,10 +4470,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117711640</v>
+        <v>117711790</v>
       </c>
       <c r="B39" t="n">
-        <v>78217</v>
+        <v>78480</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4516,21 +4486,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4540,10 +4510,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>465566</v>
+        <v>465200</v>
       </c>
       <c r="R39" t="n">
-        <v>6822693</v>
+        <v>6823139</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4602,10 +4572,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117711684</v>
+        <v>117711446</v>
       </c>
       <c r="B40" t="n">
-        <v>79521</v>
+        <v>79098</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4614,25 +4584,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>229497</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4642,10 +4612,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>465128</v>
+        <v>465106</v>
       </c>
       <c r="R40" t="n">
-        <v>6823219</v>
+        <v>6823211</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4704,10 +4674,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117711422</v>
+        <v>117711557</v>
       </c>
       <c r="B41" t="n">
-        <v>79098</v>
+        <v>79590</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4716,38 +4686,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>465425</v>
+        <v>465117</v>
       </c>
       <c r="R41" t="n">
-        <v>6822894</v>
+        <v>6823218</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4782,12 +4755,18 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På asp</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4806,10 +4785,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117711390</v>
+        <v>117711457</v>
       </c>
       <c r="B42" t="n">
-        <v>78514</v>
+        <v>79098</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4822,21 +4801,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4846,10 +4825,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>465508</v>
+        <v>465273</v>
       </c>
       <c r="R42" t="n">
-        <v>6822804</v>
+        <v>6823001</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4908,10 +4887,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117711794</v>
+        <v>117711640</v>
       </c>
       <c r="B43" t="n">
-        <v>78480</v>
+        <v>78217</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4924,21 +4903,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4948,10 +4927,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>465131</v>
+        <v>465566</v>
       </c>
       <c r="R43" t="n">
-        <v>6823271</v>
+        <v>6822693</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5010,10 +4989,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117711702</v>
+        <v>117711635</v>
       </c>
       <c r="B44" t="n">
-        <v>78216</v>
+        <v>78217</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5026,21 +5005,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5050,10 +5029,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>465087</v>
+        <v>465508</v>
       </c>
       <c r="R44" t="n">
-        <v>6823173</v>
+        <v>6822811</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5112,10 +5091,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117711424</v>
+        <v>117711643</v>
       </c>
       <c r="B45" t="n">
-        <v>79098</v>
+        <v>78217</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5128,21 +5107,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5152,10 +5131,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>465540</v>
+        <v>465750</v>
       </c>
       <c r="R45" t="n">
-        <v>6822684</v>
+        <v>6822474</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5214,7 +5193,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117711986</v>
+        <v>117711984</v>
       </c>
       <c r="B46" t="n">
         <v>78125</v>
@@ -5254,10 +5233,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>465243</v>
+        <v>465482</v>
       </c>
       <c r="R46" t="n">
-        <v>6823070</v>
+        <v>6822757</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5316,10 +5295,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117711985</v>
+        <v>117711691</v>
       </c>
       <c r="B47" t="n">
-        <v>78125</v>
+        <v>78216</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5332,21 +5311,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5356,10 +5335,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>465375</v>
+        <v>465564</v>
       </c>
       <c r="R47" t="n">
-        <v>6822775</v>
+        <v>6822699</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5418,7 +5397,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117711816</v>
+        <v>117711793</v>
       </c>
       <c r="B48" t="n">
         <v>78480</v>
@@ -5458,10 +5437,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>465243</v>
+        <v>465118</v>
       </c>
       <c r="R48" t="n">
-        <v>6822961</v>
+        <v>6823227</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5520,10 +5499,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117711815</v>
+        <v>117711597</v>
       </c>
       <c r="B49" t="n">
-        <v>78480</v>
+        <v>57287</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5536,34 +5515,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>465352</v>
+        <v>465248</v>
       </c>
       <c r="R49" t="n">
-        <v>6823213</v>
+        <v>6823304</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5596,6 +5583,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5622,10 +5614,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117711687</v>
+        <v>117711522</v>
       </c>
       <c r="B50" t="n">
-        <v>78216</v>
+        <v>79069</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5638,21 +5630,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5662,10 +5654,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>465515</v>
+        <v>465398</v>
       </c>
       <c r="R50" t="n">
-        <v>6822687</v>
+        <v>6822828</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5724,7 +5716,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117711418</v>
+        <v>117711435</v>
       </c>
       <c r="B51" t="n">
         <v>79098</v>
@@ -5764,10 +5756,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>465512</v>
+        <v>465796</v>
       </c>
       <c r="R51" t="n">
-        <v>6822691</v>
+        <v>6822437</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5826,10 +5818,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117711643</v>
+        <v>117711437</v>
       </c>
       <c r="B52" t="n">
-        <v>78217</v>
+        <v>79098</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5842,21 +5834,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5866,10 +5858,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>465750</v>
+        <v>465604</v>
       </c>
       <c r="R52" t="n">
-        <v>6822474</v>
+        <v>6822495</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5928,10 +5920,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117711626</v>
+        <v>117711387</v>
       </c>
       <c r="B53" t="n">
-        <v>78217</v>
+        <v>78514</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5944,21 +5936,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5968,10 +5960,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>465453</v>
+        <v>465419</v>
       </c>
       <c r="R53" t="n">
-        <v>6822624</v>
+        <v>6822910</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6030,10 +6022,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>117711528</v>
+        <v>117711602</v>
       </c>
       <c r="B54" t="n">
-        <v>78579</v>
+        <v>57287</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6046,34 +6038,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>967</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>465164</v>
+        <v>465318</v>
       </c>
       <c r="R54" t="n">
-        <v>6823206</v>
+        <v>6823263</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6106,6 +6106,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6132,10 +6137,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>117711689</v>
+        <v>117711399</v>
       </c>
       <c r="B55" t="n">
-        <v>78216</v>
+        <v>78514</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6148,21 +6153,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6172,10 +6177,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>465373</v>
+        <v>465258</v>
       </c>
       <c r="R55" t="n">
-        <v>6822775</v>
+        <v>6823270</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6234,10 +6239,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>117711452</v>
+        <v>117711810</v>
       </c>
       <c r="B56" t="n">
-        <v>79098</v>
+        <v>78480</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6250,21 +6255,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6274,10 +6279,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>465263</v>
+        <v>465284</v>
       </c>
       <c r="R56" t="n">
-        <v>6823399</v>
+        <v>6823283</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6336,10 +6341,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>117711744</v>
+        <v>117711733</v>
       </c>
       <c r="B57" t="n">
-        <v>78480</v>
+        <v>90517</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6352,21 +6357,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6376,10 +6381,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>465439</v>
+        <v>465286</v>
       </c>
       <c r="R57" t="n">
-        <v>6822881</v>
+        <v>6823284</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6438,10 +6443,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>117711442</v>
+        <v>117711815</v>
       </c>
       <c r="B58" t="n">
-        <v>79098</v>
+        <v>78480</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6454,21 +6459,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6478,10 +6483,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>465158</v>
+        <v>465352</v>
       </c>
       <c r="R58" t="n">
-        <v>6823203</v>
+        <v>6823213</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6540,7 +6545,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>117711806</v>
+        <v>117711745</v>
       </c>
       <c r="B59" t="n">
         <v>78480</v>
@@ -6580,10 +6585,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>465257</v>
+        <v>465507</v>
       </c>
       <c r="R59" t="n">
-        <v>6823277</v>
+        <v>6822804</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6642,7 +6647,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>117711447</v>
+        <v>117711443</v>
       </c>
       <c r="B60" t="n">
         <v>79098</v>
@@ -6682,10 +6687,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>465137</v>
+        <v>465047</v>
       </c>
       <c r="R60" t="n">
-        <v>6823348</v>
+        <v>6823271</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6744,10 +6749,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>117711453</v>
+        <v>117711701</v>
       </c>
       <c r="B61" t="n">
-        <v>79098</v>
+        <v>78216</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6760,21 +6765,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6784,10 +6789,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>465228</v>
+        <v>465157</v>
       </c>
       <c r="R61" t="n">
-        <v>6823410</v>
+        <v>6823202</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6846,10 +6851,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>117711645</v>
+        <v>117711423</v>
       </c>
       <c r="B62" t="n">
-        <v>78217</v>
+        <v>79098</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6862,21 +6867,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6886,10 +6891,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>465796</v>
+        <v>465448</v>
       </c>
       <c r="R62" t="n">
-        <v>6822437</v>
+        <v>6822872</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6948,10 +6953,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>117711627</v>
+        <v>117711536</v>
       </c>
       <c r="B63" t="n">
-        <v>78217</v>
+        <v>57287</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6964,34 +6969,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>465477</v>
+        <v>465650</v>
       </c>
       <c r="R63" t="n">
-        <v>6822612</v>
+        <v>6822573</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7024,6 +7037,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7050,10 +7068,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>117711417</v>
+        <v>117711648</v>
       </c>
       <c r="B64" t="n">
-        <v>79098</v>
+        <v>78217</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7066,21 +7084,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7090,10 +7108,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>465453</v>
+        <v>465691</v>
       </c>
       <c r="R64" t="n">
-        <v>6822624</v>
+        <v>6822493</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7152,10 +7170,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>117711629</v>
+        <v>117711579</v>
       </c>
       <c r="B65" t="n">
-        <v>78217</v>
+        <v>57303</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7168,34 +7186,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>465398</v>
+        <v>465419</v>
       </c>
       <c r="R65" t="n">
-        <v>6822827</v>
+        <v>6822900</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7254,10 +7280,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>117711693</v>
+        <v>117711791</v>
       </c>
       <c r="B66" t="n">
-        <v>78216</v>
+        <v>78480</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7270,21 +7296,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7294,10 +7320,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>465629</v>
+        <v>465146</v>
       </c>
       <c r="R66" t="n">
-        <v>6822491</v>
+        <v>6823190</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7356,10 +7382,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>117711434</v>
+        <v>117711802</v>
       </c>
       <c r="B67" t="n">
-        <v>79098</v>
+        <v>78480</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7372,21 +7398,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7396,10 +7422,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>465812</v>
+        <v>465271</v>
       </c>
       <c r="R67" t="n">
-        <v>6822424</v>
+        <v>6823388</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7458,10 +7484,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>117711456</v>
+        <v>117711630</v>
       </c>
       <c r="B68" t="n">
-        <v>79098</v>
+        <v>78217</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7474,21 +7500,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7498,10 +7524,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>465353</v>
+        <v>465362</v>
       </c>
       <c r="R68" t="n">
-        <v>6823194</v>
+        <v>6822857</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7560,10 +7586,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>117711690</v>
+        <v>117711988</v>
       </c>
       <c r="B69" t="n">
-        <v>78216</v>
+        <v>78125</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7576,21 +7602,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7600,10 +7626,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>465540</v>
+        <v>465229</v>
       </c>
       <c r="R69" t="n">
-        <v>6822684</v>
+        <v>6823280</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7662,7 +7688,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>117711429</v>
+        <v>117711434</v>
       </c>
       <c r="B70" t="n">
         <v>79098</v>
@@ -7702,10 +7728,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>465655</v>
+        <v>465812</v>
       </c>
       <c r="R70" t="n">
-        <v>6822559</v>
+        <v>6822424</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7764,7 +7790,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>117711433</v>
+        <v>117711424</v>
       </c>
       <c r="B71" t="n">
         <v>79098</v>
@@ -7804,10 +7830,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>465750</v>
+        <v>465540</v>
       </c>
       <c r="R71" t="n">
-        <v>6822471</v>
+        <v>6822684</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7866,10 +7892,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>117711437</v>
+        <v>117711645</v>
       </c>
       <c r="B72" t="n">
-        <v>79098</v>
+        <v>78217</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7882,21 +7908,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7906,10 +7932,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>465604</v>
+        <v>465796</v>
       </c>
       <c r="R72" t="n">
-        <v>6822495</v>
+        <v>6822437</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7968,10 +7994,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>117711733</v>
+        <v>117711654</v>
       </c>
       <c r="B73" t="n">
-        <v>90517</v>
+        <v>78217</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7984,21 +8010,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5432</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8008,10 +8034,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>465286</v>
+        <v>465036</v>
       </c>
       <c r="R73" t="n">
-        <v>6823284</v>
+        <v>6823260</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8070,10 +8096,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>117711637</v>
+        <v>117711426</v>
       </c>
       <c r="B74" t="n">
-        <v>78217</v>
+        <v>79098</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8086,21 +8112,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8110,10 +8136,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>465540</v>
+        <v>465566</v>
       </c>
       <c r="R74" t="n">
-        <v>6822684</v>
+        <v>6822693</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8172,10 +8198,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>117711635</v>
+        <v>117711742</v>
       </c>
       <c r="B75" t="n">
-        <v>78217</v>
+        <v>78480</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8188,21 +8214,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8212,10 +8238,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>465508</v>
+        <v>465389</v>
       </c>
       <c r="R75" t="n">
-        <v>6822811</v>
+        <v>6822818</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8274,10 +8300,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>117711691</v>
+        <v>117711743</v>
       </c>
       <c r="B76" t="n">
-        <v>78216</v>
+        <v>78480</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8290,21 +8316,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8314,10 +8340,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>465564</v>
+        <v>465421</v>
       </c>
       <c r="R76" t="n">
-        <v>6822699</v>
+        <v>6822897</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8376,10 +8402,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>117711802</v>
+        <v>117711456</v>
       </c>
       <c r="B77" t="n">
-        <v>78480</v>
+        <v>79098</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8392,21 +8418,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8416,10 +8442,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>465271</v>
+        <v>465353</v>
       </c>
       <c r="R77" t="n">
-        <v>6823388</v>
+        <v>6823194</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8478,10 +8504,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>117711436</v>
+        <v>117711702</v>
       </c>
       <c r="B78" t="n">
-        <v>79098</v>
+        <v>78216</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8494,21 +8520,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8518,10 +8544,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>465689</v>
+        <v>465087</v>
       </c>
       <c r="R78" t="n">
-        <v>6822499</v>
+        <v>6823173</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8580,10 +8606,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>117711602</v>
+        <v>117711444</v>
       </c>
       <c r="B79" t="n">
-        <v>57287</v>
+        <v>79098</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8596,42 +8622,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>465318</v>
+        <v>465036</v>
       </c>
       <c r="R79" t="n">
-        <v>6823263</v>
+        <v>6823260</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8664,11 +8682,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-06-10</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8695,10 +8708,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>117711579</v>
+        <v>117711544</v>
       </c>
       <c r="B80" t="n">
-        <v>57303</v>
+        <v>56499</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8707,25 +8720,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8733,7 +8746,7 @@
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
@@ -8743,10 +8756,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>465419</v>
+        <v>465222</v>
       </c>
       <c r="R80" t="n">
-        <v>6822900</v>
+        <v>6823415</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8805,10 +8818,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>117711654</v>
+        <v>117711418</v>
       </c>
       <c r="B81" t="n">
-        <v>78217</v>
+        <v>79098</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8821,21 +8834,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8845,10 +8858,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>465036</v>
+        <v>465512</v>
       </c>
       <c r="R81" t="n">
-        <v>6823260</v>
+        <v>6822691</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8907,10 +8920,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>117711632</v>
+        <v>117711422</v>
       </c>
       <c r="B82" t="n">
-        <v>78217</v>
+        <v>79098</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8923,21 +8936,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8947,10 +8960,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>465365</v>
+        <v>465425</v>
       </c>
       <c r="R82" t="n">
-        <v>6822944</v>
+        <v>6822894</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9009,10 +9022,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>117711646</v>
+        <v>117711445</v>
       </c>
       <c r="B83" t="n">
-        <v>78217</v>
+        <v>79098</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9025,21 +9038,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9049,10 +9062,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>465771</v>
+        <v>465092</v>
       </c>
       <c r="R83" t="n">
-        <v>6822442</v>
+        <v>6823189</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9111,10 +9124,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>117711401</v>
+        <v>117711705</v>
       </c>
       <c r="B84" t="n">
-        <v>78514</v>
+        <v>78216</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9127,21 +9140,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9151,10 +9164,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>465340</v>
+        <v>465295</v>
       </c>
       <c r="R84" t="n">
-        <v>6823249</v>
+        <v>6823402</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9213,10 +9226,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>117711745</v>
+        <v>117711631</v>
       </c>
       <c r="B85" t="n">
-        <v>78480</v>
+        <v>78217</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9229,21 +9242,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9253,10 +9266,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>465507</v>
+        <v>465358</v>
       </c>
       <c r="R85" t="n">
-        <v>6822804</v>
+        <v>6822917</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9315,10 +9328,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>117711805</v>
+        <v>117711398</v>
       </c>
       <c r="B86" t="n">
-        <v>78480</v>
+        <v>78514</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9331,21 +9344,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9355,10 +9368,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>465244</v>
+        <v>465275</v>
       </c>
       <c r="R86" t="n">
-        <v>6823294</v>
+        <v>6823367</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9417,10 +9430,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>117711742</v>
+        <v>117711528</v>
       </c>
       <c r="B87" t="n">
-        <v>78480</v>
+        <v>78579</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9433,21 +9446,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>967</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9457,10 +9470,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>465389</v>
+        <v>465164</v>
       </c>
       <c r="R87" t="n">
-        <v>6822818</v>
+        <v>6823206</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9519,10 +9532,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>117711435</v>
+        <v>117711741</v>
       </c>
       <c r="B88" t="n">
-        <v>79098</v>
+        <v>78480</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9535,21 +9548,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9559,10 +9572,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>465796</v>
+        <v>465468</v>
       </c>
       <c r="R88" t="n">
-        <v>6822437</v>
+        <v>6822605</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9621,10 +9634,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>117700533</v>
+        <v>117711804</v>
       </c>
       <c r="B89" t="n">
-        <v>79590</v>
+        <v>78480</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9633,38 +9646,38 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Stygguggen, Orsa, Dlr</t>
+          <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>465554</v>
+        <v>465229</v>
       </c>
       <c r="R89" t="n">
-        <v>6822711</v>
+        <v>6823280</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9708,40 +9721,25 @@
       <c r="AG89" t="b">
         <v>0</v>
       </c>
-      <c r="AJ89" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK89" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO89" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>117711527</v>
+        <v>117711806</v>
       </c>
       <c r="B90" t="n">
-        <v>78579</v>
+        <v>78480</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9754,37 +9752,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>465397</v>
+        <v>465257</v>
       </c>
       <c r="R90" t="n">
-        <v>6822826</v>
+        <v>6823277</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9819,18 +9814,12 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -9849,10 +9838,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>117711984</v>
+        <v>117711453</v>
       </c>
       <c r="B91" t="n">
-        <v>78125</v>
+        <v>79098</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9865,21 +9854,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9889,10 +9878,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>465482</v>
+        <v>465228</v>
       </c>
       <c r="R91" t="n">
-        <v>6822757</v>
+        <v>6823410</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9951,10 +9940,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>117711707</v>
+        <v>117711386</v>
       </c>
       <c r="B92" t="n">
-        <v>78216</v>
+        <v>78514</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9967,21 +9956,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9991,10 +9980,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>465368</v>
+        <v>465484</v>
       </c>
       <c r="R92" t="n">
-        <v>6823128</v>
+        <v>6822737</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10053,10 +10042,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>117711704</v>
+        <v>117711530</v>
       </c>
       <c r="B93" t="n">
-        <v>78216</v>
+        <v>90499</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10069,21 +10058,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10093,10 +10082,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>465197</v>
+        <v>465283</v>
       </c>
       <c r="R93" t="n">
-        <v>6823333</v>
+        <v>6823280</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10155,7 +10144,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>117711741</v>
+        <v>117711813</v>
       </c>
       <c r="B94" t="n">
         <v>78480</v>
@@ -10195,10 +10184,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>465468</v>
+        <v>465306</v>
       </c>
       <c r="R94" t="n">
-        <v>6822605</v>
+        <v>6823279</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10257,10 +10246,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>117711631</v>
+        <v>117711688</v>
       </c>
       <c r="B95" t="n">
-        <v>78217</v>
+        <v>78216</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10273,21 +10262,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10297,10 +10286,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>465358</v>
+        <v>465494</v>
       </c>
       <c r="R95" t="n">
-        <v>6822917</v>
+        <v>6822741</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10359,10 +10348,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>117711606</v>
+        <v>117711432</v>
       </c>
       <c r="B96" t="n">
-        <v>96797</v>
+        <v>79098</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10371,25 +10360,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10399,10 +10388,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>465576</v>
+        <v>465744</v>
       </c>
       <c r="R96" t="n">
-        <v>6822530</v>
+        <v>6822471</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10461,10 +10450,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>117711682</v>
+        <v>117711692</v>
       </c>
       <c r="B97" t="n">
-        <v>80437</v>
+        <v>78216</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10477,21 +10466,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1049</v>
+        <v>6446</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10501,7 +10490,7 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>465659</v>
+        <v>465656</v>
       </c>
       <c r="R97" t="n">
         <v>6822514</v>
@@ -10563,10 +10552,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>117711703</v>
+        <v>117711429</v>
       </c>
       <c r="B98" t="n">
-        <v>78216</v>
+        <v>79098</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10579,21 +10568,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10603,10 +10592,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>465145</v>
+        <v>465655</v>
       </c>
       <c r="R98" t="n">
-        <v>6823279</v>
+        <v>6822559</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10665,10 +10654,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>117711692</v>
+        <v>117711592</v>
       </c>
       <c r="B99" t="n">
-        <v>78216</v>
+        <v>57287</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10681,34 +10670,42 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>465656</v>
+        <v>465242</v>
       </c>
       <c r="R99" t="n">
-        <v>6822514</v>
+        <v>6822897</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10741,6 +10738,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10767,10 +10769,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>117711441</v>
+        <v>117711985</v>
       </c>
       <c r="B100" t="n">
-        <v>79098</v>
+        <v>78125</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10783,21 +10785,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10807,10 +10809,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>465167</v>
+        <v>465375</v>
       </c>
       <c r="R100" t="n">
-        <v>6823048</v>
+        <v>6822775</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10869,10 +10871,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>117711545</v>
+        <v>117711683</v>
       </c>
       <c r="B101" t="n">
-        <v>56499</v>
+        <v>80437</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10881,46 +10883,38 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100138</v>
+        <v>1049</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>465578</v>
+        <v>465335</v>
       </c>
       <c r="R101" t="n">
-        <v>6822532</v>
+        <v>6823378</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10979,10 +10973,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>117711399</v>
+        <v>117712002</v>
       </c>
       <c r="B102" t="n">
-        <v>78514</v>
+        <v>91772</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10991,25 +10985,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11019,10 +11013,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>465258</v>
+        <v>465293</v>
       </c>
       <c r="R102" t="n">
-        <v>6823270</v>
+        <v>6823387</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11081,10 +11075,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>117711391</v>
+        <v>117711606</v>
       </c>
       <c r="B103" t="n">
-        <v>78514</v>
+        <v>96797</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11093,25 +11087,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>185</v>
+        <v>221941</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11121,10 +11115,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>465658</v>
+        <v>465576</v>
       </c>
       <c r="R103" t="n">
-        <v>6822562</v>
+        <v>6822530</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11183,10 +11177,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>117711790</v>
+        <v>117711388</v>
       </c>
       <c r="B104" t="n">
-        <v>78480</v>
+        <v>78514</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11199,21 +11193,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11223,10 +11217,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>465200</v>
+        <v>465465</v>
       </c>
       <c r="R104" t="n">
-        <v>6823139</v>
+        <v>6822863</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11285,10 +11279,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>117711799</v>
+        <v>117711401</v>
       </c>
       <c r="B105" t="n">
-        <v>78480</v>
+        <v>78514</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11301,21 +11295,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11325,10 +11319,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>465272</v>
+        <v>465340</v>
       </c>
       <c r="R105" t="n">
-        <v>6823356</v>
+        <v>6823249</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11387,10 +11381,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>117711793</v>
+        <v>117711436</v>
       </c>
       <c r="B106" t="n">
-        <v>78480</v>
+        <v>79098</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11403,21 +11397,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11427,10 +11421,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>465118</v>
+        <v>465689</v>
       </c>
       <c r="R106" t="n">
-        <v>6823227</v>
+        <v>6822499</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11489,10 +11483,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>117711648</v>
+        <v>117711690</v>
       </c>
       <c r="B107" t="n">
-        <v>78217</v>
+        <v>78216</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11505,21 +11499,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11529,10 +11523,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>465691</v>
+        <v>465540</v>
       </c>
       <c r="R107" t="n">
-        <v>6822493</v>
+        <v>6822684</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11591,10 +11585,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>117712010</v>
+        <v>117711687</v>
       </c>
       <c r="B108" t="n">
-        <v>77864</v>
+        <v>78216</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11607,21 +11601,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11631,10 +11625,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>465658</v>
+        <v>465515</v>
       </c>
       <c r="R108" t="n">
-        <v>6822513</v>
+        <v>6822687</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11693,10 +11687,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>117712009</v>
+        <v>117700533</v>
       </c>
       <c r="B109" t="n">
-        <v>77864</v>
+        <v>79590</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11705,38 +11699,38 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6437</v>
+        <v>6462</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Stygguggen, Dlr</t>
+          <t>Stygguggen, Orsa, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>465568</v>
+        <v>465554</v>
       </c>
       <c r="R109" t="n">
-        <v>6822697</v>
+        <v>6822711</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11780,25 +11774,40 @@
       <c r="AG109" t="b">
         <v>0</v>
       </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>117711536</v>
+        <v>117711638</v>
       </c>
       <c r="B110" t="n">
-        <v>57287</v>
+        <v>78217</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11811,42 +11820,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>465650</v>
+        <v>465540</v>
       </c>
       <c r="R110" t="n">
-        <v>6822573</v>
+        <v>6822682</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11879,11 +11880,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2024-06-10</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11910,7 +11906,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>117711638</v>
+        <v>117711632</v>
       </c>
       <c r="B111" t="n">
         <v>78217</v>
@@ -11950,10 +11946,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>465540</v>
+        <v>465365</v>
       </c>
       <c r="R111" t="n">
-        <v>6822682</v>
+        <v>6822944</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12012,10 +12008,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>117711530</v>
+        <v>117711646</v>
       </c>
       <c r="B112" t="n">
-        <v>90499</v>
+        <v>78217</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12028,21 +12024,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12052,10 +12048,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>465283</v>
+        <v>465771</v>
       </c>
       <c r="R112" t="n">
-        <v>6823280</v>
+        <v>6822442</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12114,10 +12110,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>117711743</v>
+        <v>117711689</v>
       </c>
       <c r="B113" t="n">
-        <v>78480</v>
+        <v>78216</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12130,21 +12126,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12154,10 +12150,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>465421</v>
+        <v>465373</v>
       </c>
       <c r="R113" t="n">
-        <v>6822897</v>
+        <v>6822775</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12216,7 +12212,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>117711688</v>
+        <v>117711685</v>
       </c>
       <c r="B114" t="n">
         <v>78216</v>
@@ -12250,16 +12246,23 @@
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>465494</v>
+        <v>465797</v>
       </c>
       <c r="R114" t="n">
-        <v>6822741</v>
+        <v>6822438</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12300,6 +12303,7 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -12318,10 +12322,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>117711420</v>
+        <v>117711707</v>
       </c>
       <c r="B115" t="n">
-        <v>79098</v>
+        <v>78216</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12334,21 +12338,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12358,10 +12362,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>465373</v>
+        <v>465368</v>
       </c>
       <c r="R115" t="n">
-        <v>6822775</v>
+        <v>6823128</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12420,7 +12424,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>117711432</v>
+        <v>117711431</v>
       </c>
       <c r="B116" t="n">
         <v>79098</v>
@@ -12460,10 +12464,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>465744</v>
+        <v>465700</v>
       </c>
       <c r="R116" t="n">
-        <v>6822471</v>
+        <v>6822497</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12522,10 +12526,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>117711455</v>
+        <v>117711636</v>
       </c>
       <c r="B117" t="n">
-        <v>79098</v>
+        <v>78217</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12538,21 +12542,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12562,10 +12566,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>465215</v>
+        <v>465528</v>
       </c>
       <c r="R117" t="n">
-        <v>6823375</v>
+        <v>6822701</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12624,10 +12628,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>117712002</v>
+        <v>117711634</v>
       </c>
       <c r="B118" t="n">
-        <v>91772</v>
+        <v>78217</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12636,25 +12640,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12664,10 +12668,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>465293</v>
+        <v>465448</v>
       </c>
       <c r="R118" t="n">
-        <v>6823387</v>
+        <v>6822872</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12726,10 +12730,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>117711728</v>
+        <v>117711693</v>
       </c>
       <c r="B119" t="n">
-        <v>90648</v>
+        <v>78216</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12738,25 +12742,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12766,10 +12770,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>465382</v>
+        <v>465629</v>
       </c>
       <c r="R119" t="n">
-        <v>6822811</v>
+        <v>6822491</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12828,10 +12832,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>117711628</v>
+        <v>117711704</v>
       </c>
       <c r="B120" t="n">
-        <v>78217</v>
+        <v>78216</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12844,21 +12848,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12868,10 +12872,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>465491</v>
+        <v>465197</v>
       </c>
       <c r="R120" t="n">
-        <v>6822739</v>
+        <v>6823333</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12930,10 +12934,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>117711535</v>
+        <v>117711986</v>
       </c>
       <c r="B121" t="n">
-        <v>57287</v>
+        <v>78125</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -12946,42 +12950,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>465168</v>
+        <v>465243</v>
       </c>
       <c r="R121" t="n">
-        <v>6823294</v>
+        <v>6823070</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13014,11 +13010,6 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2024-06-10</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Bo, troligen använt 2023</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13045,10 +13036,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>117711398</v>
+        <v>117711527</v>
       </c>
       <c r="B122" t="n">
-        <v>78514</v>
+        <v>78579</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13061,34 +13052,37 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>185</v>
+        <v>967</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>465275</v>
+        <v>465397</v>
       </c>
       <c r="R122" t="n">
-        <v>6823367</v>
+        <v>6822826</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13123,12 +13117,18 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -13147,10 +13147,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>117711431</v>
+        <v>117711987</v>
       </c>
       <c r="B123" t="n">
-        <v>79098</v>
+        <v>78125</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13163,21 +13163,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13187,10 +13187,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>465700</v>
+        <v>465232</v>
       </c>
       <c r="R123" t="n">
-        <v>6822497</v>
+        <v>6823416</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13249,10 +13249,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>117711804</v>
+        <v>117711400</v>
       </c>
       <c r="B124" t="n">
-        <v>78480</v>
+        <v>78514</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13265,21 +13265,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13289,10 +13289,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>465229</v>
+        <v>465326</v>
       </c>
       <c r="R124" t="n">
-        <v>6823280</v>
+        <v>6823285</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13351,10 +13351,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>117711705</v>
+        <v>117712010</v>
       </c>
       <c r="B125" t="n">
-        <v>78216</v>
+        <v>77864</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13367,21 +13367,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13391,10 +13391,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>465295</v>
+        <v>465658</v>
       </c>
       <c r="R125" t="n">
-        <v>6823402</v>
+        <v>6822513</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13453,10 +13453,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>117711706</v>
+        <v>117711442</v>
       </c>
       <c r="B126" t="n">
-        <v>78216</v>
+        <v>79098</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13469,21 +13469,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13493,10 +13493,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>465257</v>
+        <v>465158</v>
       </c>
       <c r="R126" t="n">
-        <v>6823270</v>
+        <v>6823203</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13555,7 +13555,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>117711443</v>
+        <v>117711441</v>
       </c>
       <c r="B127" t="n">
         <v>79098</v>
@@ -13595,10 +13595,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>465047</v>
+        <v>465167</v>
       </c>
       <c r="R127" t="n">
-        <v>6823271</v>
+        <v>6823048</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13657,10 +13657,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>117711451</v>
+        <v>117711649</v>
       </c>
       <c r="B128" t="n">
-        <v>79098</v>
+        <v>78217</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13673,21 +13673,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13697,10 +13697,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>465293</v>
+        <v>465644</v>
       </c>
       <c r="R128" t="n">
-        <v>6823407</v>
+        <v>6822519</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13759,10 +13759,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>117711450</v>
+        <v>117711637</v>
       </c>
       <c r="B129" t="n">
-        <v>79098</v>
+        <v>78217</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13775,21 +13775,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13799,10 +13799,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>465326</v>
+        <v>465540</v>
       </c>
       <c r="R129" t="n">
-        <v>6823374</v>
+        <v>6822684</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>

--- a/artfynd/A 47917-2023 artfynd.xlsx
+++ b/artfynd/A 47917-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117711728</v>
+        <v>117711522</v>
       </c>
       <c r="B2" t="n">
-        <v>90648</v>
+        <v>79071</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1503</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465382</v>
+        <v>465398</v>
       </c>
       <c r="R2" t="n">
-        <v>6822811</v>
+        <v>6822828</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117711795</v>
+        <v>117711648</v>
       </c>
       <c r="B3" t="n">
-        <v>78480</v>
+        <v>78219</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465163</v>
+        <v>465691</v>
       </c>
       <c r="R3" t="n">
-        <v>6823288</v>
+        <v>6822493</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117711812</v>
+        <v>117711643</v>
       </c>
       <c r="B4" t="n">
-        <v>78480</v>
+        <v>78219</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465285</v>
+        <v>465750</v>
       </c>
       <c r="R4" t="n">
-        <v>6823267</v>
+        <v>6822474</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117711451</v>
+        <v>117711693</v>
       </c>
       <c r="B5" t="n">
-        <v>79098</v>
+        <v>78218</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465293</v>
+        <v>465629</v>
       </c>
       <c r="R5" t="n">
-        <v>6823407</v>
+        <v>6822491</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
         <v>117711455</v>
       </c>
       <c r="B6" t="n">
-        <v>79098</v>
+        <v>79100</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117711425</v>
+        <v>117711419</v>
       </c>
       <c r="B7" t="n">
-        <v>79098</v>
+        <v>79100</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465537</v>
+        <v>465488</v>
       </c>
       <c r="R7" t="n">
-        <v>6822683</v>
+        <v>6822741</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117711449</v>
+        <v>117711457</v>
       </c>
       <c r="B8" t="n">
-        <v>79098</v>
+        <v>79100</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465140</v>
+        <v>465273</v>
       </c>
       <c r="R8" t="n">
-        <v>6823344</v>
+        <v>6823001</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117711686</v>
+        <v>117711592</v>
       </c>
       <c r="B9" t="n">
-        <v>78216</v>
+        <v>57288</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,34 +1405,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465453</v>
+        <v>465242</v>
       </c>
       <c r="R9" t="n">
-        <v>6822624</v>
+        <v>6822897</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1465,6 +1473,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1491,10 +1504,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117711419</v>
+        <v>117711536</v>
       </c>
       <c r="B10" t="n">
-        <v>79098</v>
+        <v>57288</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,34 +1520,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465488</v>
+        <v>465650</v>
       </c>
       <c r="R10" t="n">
-        <v>6822741</v>
+        <v>6822573</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1567,6 +1588,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,10 +1619,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117712009</v>
+        <v>117711984</v>
       </c>
       <c r="B11" t="n">
-        <v>77864</v>
+        <v>78127</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1635,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1659,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465568</v>
+        <v>465482</v>
       </c>
       <c r="R11" t="n">
-        <v>6822697</v>
+        <v>6822757</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1721,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117711545</v>
+        <v>117711806</v>
       </c>
       <c r="B12" t="n">
-        <v>56499</v>
+        <v>78482</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,46 +1733,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465578</v>
+        <v>465257</v>
       </c>
       <c r="R12" t="n">
-        <v>6822532</v>
+        <v>6823277</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,10 +1823,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117711644</v>
+        <v>117711815</v>
       </c>
       <c r="B13" t="n">
-        <v>78217</v>
+        <v>78482</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1821,21 +1839,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1845,10 +1863,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>465798</v>
+        <v>465352</v>
       </c>
       <c r="R13" t="n">
-        <v>6822436</v>
+        <v>6823213</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1907,10 +1925,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117711626</v>
+        <v>117711444</v>
       </c>
       <c r="B14" t="n">
-        <v>78217</v>
+        <v>79100</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1923,21 +1941,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1947,10 +1965,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465453</v>
+        <v>465036</v>
       </c>
       <c r="R14" t="n">
-        <v>6822624</v>
+        <v>6823260</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2009,10 +2027,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117711627</v>
+        <v>117711706</v>
       </c>
       <c r="B15" t="n">
-        <v>78217</v>
+        <v>78218</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2025,21 +2043,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2049,10 +2067,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465477</v>
+        <v>465257</v>
       </c>
       <c r="R15" t="n">
-        <v>6822612</v>
+        <v>6823270</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2111,10 +2129,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117711805</v>
+        <v>117711686</v>
       </c>
       <c r="B16" t="n">
-        <v>78480</v>
+        <v>78218</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2127,21 +2145,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2151,10 +2169,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>465244</v>
+        <v>465453</v>
       </c>
       <c r="R16" t="n">
-        <v>6823294</v>
+        <v>6822624</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2213,10 +2231,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117711794</v>
+        <v>117711441</v>
       </c>
       <c r="B17" t="n">
-        <v>78480</v>
+        <v>79100</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2229,21 +2247,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2253,10 +2271,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>465131</v>
+        <v>465167</v>
       </c>
       <c r="R17" t="n">
-        <v>6823271</v>
+        <v>6823048</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2315,10 +2333,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117711799</v>
+        <v>117711386</v>
       </c>
       <c r="B18" t="n">
-        <v>78480</v>
+        <v>78516</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2331,21 +2349,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2355,10 +2373,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>465272</v>
+        <v>465484</v>
       </c>
       <c r="R18" t="n">
-        <v>6823356</v>
+        <v>6822737</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2417,10 +2435,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117711433</v>
+        <v>117711453</v>
       </c>
       <c r="B19" t="n">
-        <v>79098</v>
+        <v>79100</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2457,10 +2475,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>465750</v>
+        <v>465228</v>
       </c>
       <c r="R19" t="n">
-        <v>6822471</v>
+        <v>6823410</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2519,10 +2537,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117711655</v>
+        <v>117711704</v>
       </c>
       <c r="B20" t="n">
-        <v>78217</v>
+        <v>78218</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2535,21 +2553,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2559,10 +2577,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>465092</v>
+        <v>465197</v>
       </c>
       <c r="R20" t="n">
-        <v>6823190</v>
+        <v>6823333</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2621,10 +2639,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117711629</v>
+        <v>117711637</v>
       </c>
       <c r="B21" t="n">
-        <v>78217</v>
+        <v>78219</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2661,10 +2679,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>465398</v>
+        <v>465540</v>
       </c>
       <c r="R21" t="n">
-        <v>6822827</v>
+        <v>6822684</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2723,10 +2741,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117711633</v>
+        <v>117711429</v>
       </c>
       <c r="B22" t="n">
-        <v>78217</v>
+        <v>79100</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2739,21 +2757,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2763,10 +2781,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>465425</v>
+        <v>465655</v>
       </c>
       <c r="R22" t="n">
-        <v>6822873</v>
+        <v>6822559</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2825,10 +2843,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117711390</v>
+        <v>117711387</v>
       </c>
       <c r="B23" t="n">
-        <v>78514</v>
+        <v>78516</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2865,10 +2883,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>465508</v>
+        <v>465419</v>
       </c>
       <c r="R23" t="n">
-        <v>6822804</v>
+        <v>6822910</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2930,7 +2948,7 @@
         <v>117711391</v>
       </c>
       <c r="B24" t="n">
-        <v>78514</v>
+        <v>78516</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3029,10 +3047,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117711682</v>
+        <v>117711795</v>
       </c>
       <c r="B25" t="n">
-        <v>80437</v>
+        <v>78482</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3045,21 +3063,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3069,10 +3087,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>465659</v>
+        <v>465163</v>
       </c>
       <c r="R25" t="n">
-        <v>6822514</v>
+        <v>6823288</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3131,10 +3149,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117711747</v>
+        <v>117711437</v>
       </c>
       <c r="B26" t="n">
-        <v>78480</v>
+        <v>79100</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3147,21 +3165,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3174,7 +3192,7 @@
         <v>465604</v>
       </c>
       <c r="R26" t="n">
-        <v>6822515</v>
+        <v>6822495</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3233,10 +3251,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117711447</v>
+        <v>117711805</v>
       </c>
       <c r="B27" t="n">
-        <v>79098</v>
+        <v>78482</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3249,21 +3267,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3273,10 +3291,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>465137</v>
+        <v>465244</v>
       </c>
       <c r="R27" t="n">
-        <v>6823348</v>
+        <v>6823294</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3335,10 +3353,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117711417</v>
+        <v>117711435</v>
       </c>
       <c r="B28" t="n">
-        <v>79098</v>
+        <v>79100</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3375,10 +3393,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>465453</v>
+        <v>465796</v>
       </c>
       <c r="R28" t="n">
-        <v>6822624</v>
+        <v>6822437</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3437,10 +3455,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117711450</v>
+        <v>117711431</v>
       </c>
       <c r="B29" t="n">
-        <v>79098</v>
+        <v>79100</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3477,10 +3495,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>465326</v>
+        <v>465700</v>
       </c>
       <c r="R29" t="n">
-        <v>6823374</v>
+        <v>6822497</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3539,10 +3557,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117711706</v>
+        <v>117711446</v>
       </c>
       <c r="B30" t="n">
-        <v>78216</v>
+        <v>79100</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3555,21 +3573,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3579,10 +3597,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>465257</v>
+        <v>465106</v>
       </c>
       <c r="R30" t="n">
-        <v>6823270</v>
+        <v>6823211</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3641,10 +3659,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117711684</v>
+        <v>117711452</v>
       </c>
       <c r="B31" t="n">
-        <v>79521</v>
+        <v>79100</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3653,25 +3671,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229497</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3681,10 +3699,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>465128</v>
+        <v>465263</v>
       </c>
       <c r="R31" t="n">
-        <v>6823219</v>
+        <v>6823399</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3743,10 +3761,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117711452</v>
+        <v>117711636</v>
       </c>
       <c r="B32" t="n">
-        <v>79098</v>
+        <v>78219</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3759,21 +3777,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3783,10 +3801,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>465263</v>
+        <v>465528</v>
       </c>
       <c r="R32" t="n">
-        <v>6823399</v>
+        <v>6822701</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3845,10 +3863,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117711744</v>
+        <v>117711528</v>
       </c>
       <c r="B33" t="n">
-        <v>78480</v>
+        <v>78581</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3861,21 +3879,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>967</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3885,10 +3903,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>465439</v>
+        <v>465164</v>
       </c>
       <c r="R33" t="n">
-        <v>6822881</v>
+        <v>6823206</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3947,10 +3965,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117711703</v>
+        <v>117711804</v>
       </c>
       <c r="B34" t="n">
-        <v>78216</v>
+        <v>78482</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3963,21 +3981,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3987,10 +4005,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>465145</v>
+        <v>465229</v>
       </c>
       <c r="R34" t="n">
-        <v>6823279</v>
+        <v>6823280</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4049,10 +4067,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117711420</v>
+        <v>117711456</v>
       </c>
       <c r="B35" t="n">
-        <v>79098</v>
+        <v>79100</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4089,10 +4107,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>465373</v>
+        <v>465353</v>
       </c>
       <c r="R35" t="n">
-        <v>6822775</v>
+        <v>6823194</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4151,10 +4169,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117711535</v>
+        <v>117711401</v>
       </c>
       <c r="B36" t="n">
-        <v>57287</v>
+        <v>78516</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4167,42 +4185,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>465168</v>
+        <v>465340</v>
       </c>
       <c r="R36" t="n">
-        <v>6823294</v>
+        <v>6823249</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4235,11 +4245,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-06-10</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Bo, troligen använt 2023</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4266,10 +4271,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117711628</v>
+        <v>117711645</v>
       </c>
       <c r="B37" t="n">
-        <v>78217</v>
+        <v>78219</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4306,10 +4311,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>465491</v>
+        <v>465796</v>
       </c>
       <c r="R37" t="n">
-        <v>6822739</v>
+        <v>6822437</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4368,10 +4373,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117711816</v>
+        <v>117711655</v>
       </c>
       <c r="B38" t="n">
-        <v>78480</v>
+        <v>78219</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4384,21 +4389,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4408,10 +4413,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>465243</v>
+        <v>465092</v>
       </c>
       <c r="R38" t="n">
-        <v>6822961</v>
+        <v>6823190</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4470,10 +4475,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117711790</v>
+        <v>117711627</v>
       </c>
       <c r="B39" t="n">
-        <v>78480</v>
+        <v>78219</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4486,21 +4491,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4510,10 +4515,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>465200</v>
+        <v>465477</v>
       </c>
       <c r="R39" t="n">
-        <v>6823139</v>
+        <v>6822612</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4572,10 +4577,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117711446</v>
+        <v>117711684</v>
       </c>
       <c r="B40" t="n">
-        <v>79098</v>
+        <v>79523</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4584,25 +4589,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>229497</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4612,10 +4617,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>465106</v>
+        <v>465128</v>
       </c>
       <c r="R40" t="n">
-        <v>6823211</v>
+        <v>6823219</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4674,10 +4679,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117711557</v>
+        <v>117711689</v>
       </c>
       <c r="B41" t="n">
-        <v>79590</v>
+        <v>78218</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4686,41 +4691,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>465117</v>
+        <v>465373</v>
       </c>
       <c r="R41" t="n">
-        <v>6823218</v>
+        <v>6822775</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4755,18 +4757,12 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På asp</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4785,10 +4781,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117711457</v>
+        <v>117711816</v>
       </c>
       <c r="B42" t="n">
-        <v>79098</v>
+        <v>78482</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4801,21 +4797,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4825,10 +4821,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>465273</v>
+        <v>465243</v>
       </c>
       <c r="R42" t="n">
-        <v>6823001</v>
+        <v>6822961</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4887,10 +4883,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117711640</v>
+        <v>117700533</v>
       </c>
       <c r="B43" t="n">
-        <v>78217</v>
+        <v>79592</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4899,38 +4895,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stygguggen, Dlr</t>
+          <t>Stygguggen, Orsa, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>465566</v>
+        <v>465554</v>
       </c>
       <c r="R43" t="n">
-        <v>6822693</v>
+        <v>6822711</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4974,25 +4970,40 @@
       <c r="AG43" t="b">
         <v>0</v>
       </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117711635</v>
+        <v>117711742</v>
       </c>
       <c r="B44" t="n">
-        <v>78217</v>
+        <v>78482</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5005,21 +5016,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5029,10 +5040,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>465508</v>
+        <v>465389</v>
       </c>
       <c r="R44" t="n">
-        <v>6822811</v>
+        <v>6822818</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5091,10 +5102,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117711643</v>
+        <v>117711701</v>
       </c>
       <c r="B45" t="n">
-        <v>78217</v>
+        <v>78218</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5107,21 +5118,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5131,10 +5142,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>465750</v>
+        <v>465157</v>
       </c>
       <c r="R45" t="n">
-        <v>6822474</v>
+        <v>6823202</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5193,10 +5204,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117711984</v>
+        <v>117711445</v>
       </c>
       <c r="B46" t="n">
-        <v>78125</v>
+        <v>79100</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5209,21 +5220,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5233,10 +5244,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>465482</v>
+        <v>465092</v>
       </c>
       <c r="R46" t="n">
-        <v>6822757</v>
+        <v>6823189</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5295,10 +5306,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117711691</v>
+        <v>117711745</v>
       </c>
       <c r="B47" t="n">
-        <v>78216</v>
+        <v>78482</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5311,21 +5322,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5335,10 +5346,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>465564</v>
+        <v>465507</v>
       </c>
       <c r="R47" t="n">
-        <v>6822699</v>
+        <v>6822804</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5397,10 +5408,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117711793</v>
+        <v>117711986</v>
       </c>
       <c r="B48" t="n">
-        <v>78480</v>
+        <v>78127</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5413,21 +5424,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5437,10 +5448,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>465118</v>
+        <v>465243</v>
       </c>
       <c r="R48" t="n">
-        <v>6823227</v>
+        <v>6823070</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5499,10 +5510,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117711597</v>
+        <v>117711728</v>
       </c>
       <c r="B49" t="n">
-        <v>57287</v>
+        <v>90650</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5511,46 +5522,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>1503</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>465248</v>
+        <v>465382</v>
       </c>
       <c r="R49" t="n">
-        <v>6823304</v>
+        <v>6822811</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5583,11 +5586,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-06-10</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5614,10 +5612,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117711522</v>
+        <v>117711579</v>
       </c>
       <c r="B50" t="n">
-        <v>79069</v>
+        <v>57304</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5630,34 +5628,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>465398</v>
+        <v>465419</v>
       </c>
       <c r="R50" t="n">
-        <v>6822828</v>
+        <v>6822900</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5716,10 +5722,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117711435</v>
+        <v>117711733</v>
       </c>
       <c r="B51" t="n">
-        <v>79098</v>
+        <v>90519</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5732,21 +5738,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5756,10 +5762,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>465796</v>
+        <v>465286</v>
       </c>
       <c r="R51" t="n">
-        <v>6822437</v>
+        <v>6823284</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5818,10 +5824,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117711437</v>
+        <v>117711705</v>
       </c>
       <c r="B52" t="n">
-        <v>79098</v>
+        <v>78218</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5834,21 +5840,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5858,10 +5864,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>465604</v>
+        <v>465295</v>
       </c>
       <c r="R52" t="n">
-        <v>6822495</v>
+        <v>6823402</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5920,10 +5926,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117711387</v>
+        <v>117711527</v>
       </c>
       <c r="B53" t="n">
-        <v>78514</v>
+        <v>78581</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5936,34 +5942,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>185</v>
+        <v>967</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>465419</v>
+        <v>465397</v>
       </c>
       <c r="R53" t="n">
-        <v>6822910</v>
+        <v>6822826</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5998,12 +6007,18 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6022,10 +6037,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>117711602</v>
+        <v>117711535</v>
       </c>
       <c r="B54" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6060,7 +6075,7 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -6070,10 +6085,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>465318</v>
+        <v>465168</v>
       </c>
       <c r="R54" t="n">
-        <v>6823263</v>
+        <v>6823294</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6110,7 +6125,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Bo, troligen använt 2023</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6137,10 +6152,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>117711399</v>
+        <v>117711606</v>
       </c>
       <c r="B55" t="n">
-        <v>78514</v>
+        <v>96799</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6149,25 +6164,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>185</v>
+        <v>221941</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6177,10 +6192,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>465258</v>
+        <v>465576</v>
       </c>
       <c r="R55" t="n">
-        <v>6823270</v>
+        <v>6822530</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6239,10 +6254,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>117711810</v>
+        <v>117711644</v>
       </c>
       <c r="B56" t="n">
-        <v>78480</v>
+        <v>78219</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6255,21 +6270,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6279,10 +6294,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>465284</v>
+        <v>465798</v>
       </c>
       <c r="R56" t="n">
-        <v>6823283</v>
+        <v>6822436</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6341,10 +6356,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>117711733</v>
+        <v>117711631</v>
       </c>
       <c r="B57" t="n">
-        <v>90517</v>
+        <v>78219</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6357,21 +6372,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6381,10 +6396,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>465286</v>
+        <v>465358</v>
       </c>
       <c r="R57" t="n">
-        <v>6823284</v>
+        <v>6822917</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6443,10 +6458,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>117711815</v>
+        <v>117711683</v>
       </c>
       <c r="B58" t="n">
-        <v>78480</v>
+        <v>80439</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6459,21 +6474,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6483,10 +6498,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>465352</v>
+        <v>465335</v>
       </c>
       <c r="R58" t="n">
-        <v>6823213</v>
+        <v>6823378</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6545,10 +6560,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>117711745</v>
+        <v>117711399</v>
       </c>
       <c r="B59" t="n">
-        <v>78480</v>
+        <v>78516</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6561,21 +6576,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6585,10 +6600,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>465507</v>
+        <v>465258</v>
       </c>
       <c r="R59" t="n">
-        <v>6822804</v>
+        <v>6823270</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6647,10 +6662,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>117711443</v>
+        <v>117711692</v>
       </c>
       <c r="B60" t="n">
-        <v>79098</v>
+        <v>78218</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6663,21 +6678,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6687,10 +6702,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>465047</v>
+        <v>465656</v>
       </c>
       <c r="R60" t="n">
-        <v>6823271</v>
+        <v>6822514</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6749,10 +6764,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>117711701</v>
+        <v>117711420</v>
       </c>
       <c r="B61" t="n">
-        <v>78216</v>
+        <v>79100</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6765,21 +6780,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6789,10 +6804,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>465157</v>
+        <v>465373</v>
       </c>
       <c r="R61" t="n">
-        <v>6823202</v>
+        <v>6822775</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6851,10 +6866,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>117711423</v>
+        <v>117711425</v>
       </c>
       <c r="B62" t="n">
-        <v>79098</v>
+        <v>79100</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6891,10 +6906,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>465448</v>
+        <v>465537</v>
       </c>
       <c r="R62" t="n">
-        <v>6822872</v>
+        <v>6822683</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6953,10 +6968,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>117711536</v>
+        <v>117711426</v>
       </c>
       <c r="B63" t="n">
-        <v>57287</v>
+        <v>79100</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6969,42 +6984,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>465650</v>
+        <v>465566</v>
       </c>
       <c r="R63" t="n">
-        <v>6822573</v>
+        <v>6822693</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7037,11 +7044,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-06-10</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7068,10 +7070,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>117711648</v>
+        <v>117711799</v>
       </c>
       <c r="B64" t="n">
-        <v>78217</v>
+        <v>78482</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7084,21 +7086,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7108,10 +7110,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>465691</v>
+        <v>465272</v>
       </c>
       <c r="R64" t="n">
-        <v>6822493</v>
+        <v>6823356</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7170,10 +7172,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>117711579</v>
+        <v>117711628</v>
       </c>
       <c r="B65" t="n">
-        <v>57303</v>
+        <v>78219</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7186,42 +7188,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>465419</v>
+        <v>465491</v>
       </c>
       <c r="R65" t="n">
-        <v>6822900</v>
+        <v>6822739</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7280,10 +7274,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>117711791</v>
+        <v>117711629</v>
       </c>
       <c r="B66" t="n">
-        <v>78480</v>
+        <v>78219</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7296,21 +7290,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7320,10 +7314,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>465146</v>
+        <v>465398</v>
       </c>
       <c r="R66" t="n">
-        <v>6823190</v>
+        <v>6822827</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7382,10 +7376,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>117711802</v>
+        <v>117712002</v>
       </c>
       <c r="B67" t="n">
-        <v>78480</v>
+        <v>91774</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7394,25 +7388,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7422,10 +7416,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>465271</v>
+        <v>465293</v>
       </c>
       <c r="R67" t="n">
-        <v>6823388</v>
+        <v>6823387</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7484,10 +7478,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>117711630</v>
+        <v>117711707</v>
       </c>
       <c r="B68" t="n">
-        <v>78217</v>
+        <v>78218</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7500,21 +7494,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7524,10 +7518,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>465362</v>
+        <v>465368</v>
       </c>
       <c r="R68" t="n">
-        <v>6822857</v>
+        <v>6823128</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7586,10 +7580,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>117711988</v>
+        <v>117711794</v>
       </c>
       <c r="B69" t="n">
-        <v>78125</v>
+        <v>78482</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7602,21 +7596,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7626,10 +7620,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>465229</v>
+        <v>465131</v>
       </c>
       <c r="R69" t="n">
-        <v>6823280</v>
+        <v>6823271</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7688,10 +7682,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>117711434</v>
+        <v>117711691</v>
       </c>
       <c r="B70" t="n">
-        <v>79098</v>
+        <v>78218</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7704,21 +7698,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7728,10 +7722,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>465812</v>
+        <v>465564</v>
       </c>
       <c r="R70" t="n">
-        <v>6822424</v>
+        <v>6822699</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7790,10 +7784,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>117711424</v>
+        <v>117711432</v>
       </c>
       <c r="B71" t="n">
-        <v>79098</v>
+        <v>79100</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7830,10 +7824,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>465540</v>
+        <v>465744</v>
       </c>
       <c r="R71" t="n">
-        <v>6822684</v>
+        <v>6822471</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7892,10 +7886,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>117711645</v>
+        <v>117711743</v>
       </c>
       <c r="B72" t="n">
-        <v>78217</v>
+        <v>78482</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7908,21 +7902,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7932,10 +7926,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>465796</v>
+        <v>465421</v>
       </c>
       <c r="R72" t="n">
-        <v>6822437</v>
+        <v>6822897</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7994,10 +7988,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>117711654</v>
+        <v>117711447</v>
       </c>
       <c r="B73" t="n">
-        <v>78217</v>
+        <v>79100</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8010,21 +8004,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8034,10 +8028,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>465036</v>
+        <v>465137</v>
       </c>
       <c r="R73" t="n">
-        <v>6823260</v>
+        <v>6823348</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8096,10 +8090,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>117711426</v>
+        <v>117711646</v>
       </c>
       <c r="B74" t="n">
-        <v>79098</v>
+        <v>78219</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8112,21 +8106,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8136,10 +8130,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>465566</v>
+        <v>465771</v>
       </c>
       <c r="R74" t="n">
-        <v>6822693</v>
+        <v>6822442</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8198,10 +8192,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>117711742</v>
+        <v>117711635</v>
       </c>
       <c r="B75" t="n">
-        <v>78480</v>
+        <v>78219</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8214,21 +8208,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8238,10 +8232,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>465389</v>
+        <v>465508</v>
       </c>
       <c r="R75" t="n">
-        <v>6822818</v>
+        <v>6822811</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8300,10 +8294,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>117711743</v>
+        <v>117711702</v>
       </c>
       <c r="B76" t="n">
-        <v>78480</v>
+        <v>78218</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8316,21 +8310,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8340,10 +8334,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>465421</v>
+        <v>465087</v>
       </c>
       <c r="R76" t="n">
-        <v>6822897</v>
+        <v>6823173</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8402,10 +8396,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>117711456</v>
+        <v>117712009</v>
       </c>
       <c r="B77" t="n">
-        <v>79098</v>
+        <v>77866</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8418,21 +8412,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8442,10 +8436,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>465353</v>
+        <v>465568</v>
       </c>
       <c r="R77" t="n">
-        <v>6823194</v>
+        <v>6822697</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8504,10 +8498,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>117711702</v>
+        <v>117711744</v>
       </c>
       <c r="B78" t="n">
-        <v>78216</v>
+        <v>78482</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8520,21 +8514,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8544,10 +8538,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>465087</v>
+        <v>465439</v>
       </c>
       <c r="R78" t="n">
-        <v>6823173</v>
+        <v>6822881</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8606,10 +8600,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>117711444</v>
+        <v>117711630</v>
       </c>
       <c r="B79" t="n">
-        <v>79098</v>
+        <v>78219</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8622,21 +8616,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8646,10 +8640,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>465036</v>
+        <v>465362</v>
       </c>
       <c r="R79" t="n">
-        <v>6823260</v>
+        <v>6822857</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8708,10 +8702,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>117711544</v>
+        <v>117711685</v>
       </c>
       <c r="B80" t="n">
-        <v>56499</v>
+        <v>78218</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8720,33 +8714,32 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
@@ -8756,10 +8749,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>465222</v>
+        <v>465797</v>
       </c>
       <c r="R80" t="n">
-        <v>6823415</v>
+        <v>6822438</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8800,6 +8793,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8818,10 +8812,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>117711418</v>
+        <v>117711443</v>
       </c>
       <c r="B81" t="n">
-        <v>79098</v>
+        <v>79100</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8858,10 +8852,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>465512</v>
+        <v>465047</v>
       </c>
       <c r="R81" t="n">
-        <v>6822691</v>
+        <v>6823271</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8920,10 +8914,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>117711422</v>
+        <v>117711791</v>
       </c>
       <c r="B82" t="n">
-        <v>79098</v>
+        <v>78482</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8936,21 +8930,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8960,10 +8954,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>465425</v>
+        <v>465146</v>
       </c>
       <c r="R82" t="n">
-        <v>6822894</v>
+        <v>6823190</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9022,10 +9016,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>117711445</v>
+        <v>117711449</v>
       </c>
       <c r="B83" t="n">
-        <v>79098</v>
+        <v>79100</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9062,10 +9056,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>465092</v>
+        <v>465140</v>
       </c>
       <c r="R83" t="n">
-        <v>6823189</v>
+        <v>6823344</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9124,10 +9118,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>117711705</v>
+        <v>117711422</v>
       </c>
       <c r="B84" t="n">
-        <v>78216</v>
+        <v>79100</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9140,21 +9134,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9164,10 +9158,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>465295</v>
+        <v>465425</v>
       </c>
       <c r="R84" t="n">
-        <v>6823402</v>
+        <v>6822894</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9226,10 +9220,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>117711631</v>
+        <v>117711400</v>
       </c>
       <c r="B85" t="n">
-        <v>78217</v>
+        <v>78516</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9242,21 +9236,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9266,10 +9260,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>465358</v>
+        <v>465326</v>
       </c>
       <c r="R85" t="n">
-        <v>6822917</v>
+        <v>6823285</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9331,7 +9325,7 @@
         <v>117711398</v>
       </c>
       <c r="B86" t="n">
-        <v>78514</v>
+        <v>78516</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9430,10 +9424,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>117711528</v>
+        <v>117711703</v>
       </c>
       <c r="B87" t="n">
-        <v>78579</v>
+        <v>78218</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9446,21 +9440,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>967</v>
+        <v>6446</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9470,10 +9464,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>465164</v>
+        <v>465145</v>
       </c>
       <c r="R87" t="n">
-        <v>6823206</v>
+        <v>6823279</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9535,7 +9529,7 @@
         <v>117711741</v>
       </c>
       <c r="B88" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9634,10 +9628,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>117711804</v>
+        <v>117711810</v>
       </c>
       <c r="B89" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9674,10 +9668,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>465229</v>
+        <v>465284</v>
       </c>
       <c r="R89" t="n">
-        <v>6823280</v>
+        <v>6823283</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9736,10 +9730,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>117711806</v>
+        <v>117711436</v>
       </c>
       <c r="B90" t="n">
-        <v>78480</v>
+        <v>79100</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9752,21 +9746,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9776,10 +9770,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>465257</v>
+        <v>465689</v>
       </c>
       <c r="R90" t="n">
-        <v>6823277</v>
+        <v>6822499</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9838,10 +9832,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>117711453</v>
+        <v>117711634</v>
       </c>
       <c r="B91" t="n">
-        <v>79098</v>
+        <v>78219</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9854,21 +9848,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9878,10 +9872,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>465228</v>
+        <v>465448</v>
       </c>
       <c r="R91" t="n">
-        <v>6823410</v>
+        <v>6822872</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9940,10 +9934,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>117711386</v>
+        <v>117711638</v>
       </c>
       <c r="B92" t="n">
-        <v>78514</v>
+        <v>78219</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9956,21 +9950,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9980,10 +9974,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>465484</v>
+        <v>465540</v>
       </c>
       <c r="R92" t="n">
-        <v>6822737</v>
+        <v>6822682</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10042,10 +10036,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>117711530</v>
+        <v>117711985</v>
       </c>
       <c r="B93" t="n">
-        <v>90499</v>
+        <v>78127</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10058,21 +10052,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1202</v>
+        <v>353</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10082,10 +10076,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>465283</v>
+        <v>465375</v>
       </c>
       <c r="R93" t="n">
-        <v>6823280</v>
+        <v>6822775</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10144,10 +10138,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>117711813</v>
+        <v>117711388</v>
       </c>
       <c r="B94" t="n">
-        <v>78480</v>
+        <v>78516</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10160,21 +10154,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10184,10 +10178,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>465306</v>
+        <v>465465</v>
       </c>
       <c r="R94" t="n">
-        <v>6823279</v>
+        <v>6822863</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10246,10 +10240,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>117711688</v>
+        <v>117711390</v>
       </c>
       <c r="B95" t="n">
-        <v>78216</v>
+        <v>78516</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10262,21 +10256,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10286,10 +10280,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>465494</v>
+        <v>465508</v>
       </c>
       <c r="R95" t="n">
-        <v>6822741</v>
+        <v>6822804</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10348,10 +10342,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>117711432</v>
+        <v>117711597</v>
       </c>
       <c r="B96" t="n">
-        <v>79098</v>
+        <v>57288</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10364,34 +10358,42 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>465744</v>
+        <v>465248</v>
       </c>
       <c r="R96" t="n">
-        <v>6822471</v>
+        <v>6823304</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10424,6 +10426,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10450,10 +10457,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>117711692</v>
+        <v>117711812</v>
       </c>
       <c r="B97" t="n">
-        <v>78216</v>
+        <v>78482</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10466,21 +10473,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10490,10 +10497,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>465656</v>
+        <v>465285</v>
       </c>
       <c r="R97" t="n">
-        <v>6822514</v>
+        <v>6823267</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10552,10 +10559,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>117711429</v>
+        <v>117711790</v>
       </c>
       <c r="B98" t="n">
-        <v>79098</v>
+        <v>78482</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10568,21 +10575,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10592,10 +10599,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>465655</v>
+        <v>465200</v>
       </c>
       <c r="R98" t="n">
-        <v>6822559</v>
+        <v>6823139</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10654,10 +10661,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>117711592</v>
+        <v>117711451</v>
       </c>
       <c r="B99" t="n">
-        <v>57287</v>
+        <v>79100</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10670,42 +10677,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>465242</v>
+        <v>465293</v>
       </c>
       <c r="R99" t="n">
-        <v>6822897</v>
+        <v>6823407</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10738,11 +10737,6 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2024-06-10</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10769,10 +10763,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>117711985</v>
+        <v>117711545</v>
       </c>
       <c r="B100" t="n">
-        <v>78125</v>
+        <v>56500</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10781,38 +10775,46 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>465375</v>
+        <v>465578</v>
       </c>
       <c r="R100" t="n">
-        <v>6822775</v>
+        <v>6822532</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10871,10 +10873,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>117711683</v>
+        <v>117711417</v>
       </c>
       <c r="B101" t="n">
-        <v>80437</v>
+        <v>79100</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10887,21 +10889,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10911,10 +10913,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>465335</v>
+        <v>465453</v>
       </c>
       <c r="R101" t="n">
-        <v>6823378</v>
+        <v>6822624</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10973,10 +10975,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>117712002</v>
+        <v>117712010</v>
       </c>
       <c r="B102" t="n">
-        <v>91772</v>
+        <v>77866</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10985,25 +10987,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11013,10 +11015,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>465293</v>
+        <v>465658</v>
       </c>
       <c r="R102" t="n">
-        <v>6823387</v>
+        <v>6822513</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11075,10 +11077,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>117711606</v>
+        <v>117711690</v>
       </c>
       <c r="B103" t="n">
-        <v>96797</v>
+        <v>78218</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11087,25 +11089,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>221941</v>
+        <v>6446</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11115,10 +11117,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>465576</v>
+        <v>465540</v>
       </c>
       <c r="R103" t="n">
-        <v>6822530</v>
+        <v>6822684</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11177,10 +11179,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>117711388</v>
+        <v>117711433</v>
       </c>
       <c r="B104" t="n">
-        <v>78514</v>
+        <v>79100</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11193,21 +11195,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11217,10 +11219,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>465465</v>
+        <v>465750</v>
       </c>
       <c r="R104" t="n">
-        <v>6822863</v>
+        <v>6822471</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11279,10 +11281,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>117711401</v>
+        <v>117711649</v>
       </c>
       <c r="B105" t="n">
-        <v>78514</v>
+        <v>78219</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11295,21 +11297,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11319,10 +11321,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>465340</v>
+        <v>465644</v>
       </c>
       <c r="R105" t="n">
-        <v>6823249</v>
+        <v>6822519</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11381,10 +11383,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>117711436</v>
+        <v>117711640</v>
       </c>
       <c r="B106" t="n">
-        <v>79098</v>
+        <v>78219</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11397,21 +11399,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11421,10 +11423,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>465689</v>
+        <v>465566</v>
       </c>
       <c r="R106" t="n">
-        <v>6822499</v>
+        <v>6822693</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11483,10 +11485,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>117711690</v>
+        <v>117711626</v>
       </c>
       <c r="B107" t="n">
-        <v>78216</v>
+        <v>78219</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11499,21 +11501,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11523,10 +11525,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>465540</v>
+        <v>465453</v>
       </c>
       <c r="R107" t="n">
-        <v>6822684</v>
+        <v>6822624</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11585,10 +11587,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>117711687</v>
+        <v>117711813</v>
       </c>
       <c r="B108" t="n">
-        <v>78216</v>
+        <v>78482</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11601,21 +11603,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11625,10 +11627,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>465515</v>
+        <v>465306</v>
       </c>
       <c r="R108" t="n">
-        <v>6822687</v>
+        <v>6823279</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11687,10 +11689,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>117700533</v>
+        <v>117711747</v>
       </c>
       <c r="B109" t="n">
-        <v>79590</v>
+        <v>78482</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11699,38 +11701,38 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Stygguggen, Orsa, Dlr</t>
+          <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>465554</v>
+        <v>465604</v>
       </c>
       <c r="R109" t="n">
-        <v>6822711</v>
+        <v>6822515</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11774,40 +11776,25 @@
       <c r="AG109" t="b">
         <v>0</v>
       </c>
-      <c r="AJ109" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK109" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO109" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>117711638</v>
+        <v>117711434</v>
       </c>
       <c r="B110" t="n">
-        <v>78217</v>
+        <v>79100</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11820,21 +11807,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11844,10 +11831,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>465540</v>
+        <v>465812</v>
       </c>
       <c r="R110" t="n">
-        <v>6822682</v>
+        <v>6822424</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11906,10 +11893,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>117711632</v>
+        <v>117711450</v>
       </c>
       <c r="B111" t="n">
-        <v>78217</v>
+        <v>79100</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11922,21 +11909,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11946,10 +11933,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>465365</v>
+        <v>465326</v>
       </c>
       <c r="R111" t="n">
-        <v>6822944</v>
+        <v>6823374</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12008,10 +11995,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>117711646</v>
+        <v>117711687</v>
       </c>
       <c r="B112" t="n">
-        <v>78217</v>
+        <v>78218</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12024,21 +12011,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12048,10 +12035,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>465771</v>
+        <v>465515</v>
       </c>
       <c r="R112" t="n">
-        <v>6822442</v>
+        <v>6822687</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12110,10 +12097,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>117711689</v>
+        <v>117711793</v>
       </c>
       <c r="B113" t="n">
-        <v>78216</v>
+        <v>78482</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12126,21 +12113,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12150,10 +12137,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>465373</v>
+        <v>465118</v>
       </c>
       <c r="R113" t="n">
-        <v>6822775</v>
+        <v>6823227</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12212,10 +12199,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>117711685</v>
+        <v>117711988</v>
       </c>
       <c r="B114" t="n">
-        <v>78216</v>
+        <v>78127</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12228,41 +12215,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>465797</v>
+        <v>465229</v>
       </c>
       <c r="R114" t="n">
-        <v>6822438</v>
+        <v>6823280</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12303,7 +12283,6 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -12322,10 +12301,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>117711707</v>
+        <v>117711418</v>
       </c>
       <c r="B115" t="n">
-        <v>78216</v>
+        <v>79100</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12338,21 +12317,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12362,10 +12341,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>465368</v>
+        <v>465512</v>
       </c>
       <c r="R115" t="n">
-        <v>6823128</v>
+        <v>6822691</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12424,10 +12403,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>117711431</v>
+        <v>117711802</v>
       </c>
       <c r="B116" t="n">
-        <v>79098</v>
+        <v>78482</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12440,21 +12419,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12464,10 +12443,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>465700</v>
+        <v>465271</v>
       </c>
       <c r="R116" t="n">
-        <v>6822497</v>
+        <v>6823388</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12526,10 +12505,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>117711636</v>
+        <v>117711423</v>
       </c>
       <c r="B117" t="n">
-        <v>78217</v>
+        <v>79100</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12542,21 +12521,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12566,10 +12545,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>465528</v>
+        <v>465448</v>
       </c>
       <c r="R117" t="n">
-        <v>6822701</v>
+        <v>6822872</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12628,10 +12607,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>117711634</v>
+        <v>117711442</v>
       </c>
       <c r="B118" t="n">
-        <v>78217</v>
+        <v>79100</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12644,21 +12623,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12668,10 +12647,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>465448</v>
+        <v>465158</v>
       </c>
       <c r="R118" t="n">
-        <v>6822872</v>
+        <v>6823203</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12730,10 +12709,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>117711693</v>
+        <v>117711544</v>
       </c>
       <c r="B119" t="n">
-        <v>78216</v>
+        <v>56500</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12742,38 +12721,46 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>465629</v>
+        <v>465222</v>
       </c>
       <c r="R119" t="n">
-        <v>6822491</v>
+        <v>6823415</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12832,10 +12819,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>117711704</v>
+        <v>117711602</v>
       </c>
       <c r="B120" t="n">
-        <v>78216</v>
+        <v>57288</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12848,34 +12835,42 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>465197</v>
+        <v>465318</v>
       </c>
       <c r="R120" t="n">
-        <v>6823333</v>
+        <v>6823263</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12908,6 +12903,11 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12934,10 +12934,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>117711986</v>
+        <v>117711654</v>
       </c>
       <c r="B121" t="n">
-        <v>78125</v>
+        <v>78219</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -12950,21 +12950,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12974,10 +12974,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>465243</v>
+        <v>465036</v>
       </c>
       <c r="R121" t="n">
-        <v>6823070</v>
+        <v>6823260</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13036,10 +13036,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>117711527</v>
+        <v>117711688</v>
       </c>
       <c r="B122" t="n">
-        <v>78579</v>
+        <v>78218</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13052,37 +13052,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>967</v>
+        <v>6446</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>465397</v>
+        <v>465494</v>
       </c>
       <c r="R122" t="n">
-        <v>6822826</v>
+        <v>6822741</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13117,18 +13114,12 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -13147,10 +13138,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>117711987</v>
+        <v>117711424</v>
       </c>
       <c r="B123" t="n">
-        <v>78125</v>
+        <v>79100</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13163,21 +13154,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13187,10 +13178,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>465232</v>
+        <v>465540</v>
       </c>
       <c r="R123" t="n">
-        <v>6823416</v>
+        <v>6822684</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13249,10 +13240,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>117711400</v>
+        <v>117711557</v>
       </c>
       <c r="B124" t="n">
-        <v>78514</v>
+        <v>79592</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13261,38 +13252,41 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>185</v>
+        <v>6462</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>465326</v>
+        <v>465117</v>
       </c>
       <c r="R124" t="n">
-        <v>6823285</v>
+        <v>6823218</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13327,12 +13321,18 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>På asp</t>
+        </is>
+      </c>
       <c r="AD124" t="b">
         <v>0</v>
       </c>
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -13351,10 +13351,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>117712010</v>
+        <v>117711530</v>
       </c>
       <c r="B125" t="n">
-        <v>77864</v>
+        <v>90501</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13367,21 +13367,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6437</v>
+        <v>1202</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13391,10 +13391,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>465658</v>
+        <v>465283</v>
       </c>
       <c r="R125" t="n">
-        <v>6822513</v>
+        <v>6823280</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13453,10 +13453,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>117711442</v>
+        <v>117711682</v>
       </c>
       <c r="B126" t="n">
-        <v>79098</v>
+        <v>80439</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13469,21 +13469,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13493,10 +13493,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>465158</v>
+        <v>465659</v>
       </c>
       <c r="R126" t="n">
-        <v>6823203</v>
+        <v>6822514</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13555,10 +13555,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>117711441</v>
+        <v>117711987</v>
       </c>
       <c r="B127" t="n">
-        <v>79098</v>
+        <v>78127</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13571,21 +13571,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13595,10 +13595,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>465167</v>
+        <v>465232</v>
       </c>
       <c r="R127" t="n">
-        <v>6823048</v>
+        <v>6823416</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13657,10 +13657,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>117711649</v>
+        <v>117711632</v>
       </c>
       <c r="B128" t="n">
-        <v>78217</v>
+        <v>78219</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13697,10 +13697,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>465644</v>
+        <v>465365</v>
       </c>
       <c r="R128" t="n">
-        <v>6822519</v>
+        <v>6822944</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13759,10 +13759,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>117711637</v>
+        <v>117711633</v>
       </c>
       <c r="B129" t="n">
-        <v>78217</v>
+        <v>78219</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13799,10 +13799,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>465540</v>
+        <v>465425</v>
       </c>
       <c r="R129" t="n">
-        <v>6822684</v>
+        <v>6822873</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13864,7 +13864,7 @@
         <v>117711623</v>
       </c>
       <c r="B130" t="n">
-        <v>91962</v>
+        <v>91964</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>

--- a/artfynd/A 47917-2023 artfynd.xlsx
+++ b/artfynd/A 47917-2023 artfynd.xlsx
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117711592</v>
+        <v>117711984</v>
       </c>
       <c r="B9" t="n">
-        <v>57288</v>
+        <v>78127</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,42 +1405,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465242</v>
+        <v>465482</v>
       </c>
       <c r="R9" t="n">
-        <v>6822897</v>
+        <v>6822757</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1473,11 +1465,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-06-10</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1504,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117711536</v>
+        <v>117711592</v>
       </c>
       <c r="B10" t="n">
         <v>57288</v>
@@ -1552,10 +1539,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465650</v>
+        <v>465242</v>
       </c>
       <c r="R10" t="n">
-        <v>6822573</v>
+        <v>6822897</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,7 +1579,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Färskt ringhack</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1619,10 +1606,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117711984</v>
+        <v>117711536</v>
       </c>
       <c r="B11" t="n">
-        <v>78127</v>
+        <v>57288</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1635,34 +1622,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465482</v>
+        <v>465650</v>
       </c>
       <c r="R11" t="n">
-        <v>6822757</v>
+        <v>6822573</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,6 +1690,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2435,10 +2435,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117711453</v>
+        <v>117711637</v>
       </c>
       <c r="B19" t="n">
-        <v>79100</v>
+        <v>78219</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2451,21 +2451,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2475,10 +2475,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>465228</v>
+        <v>465540</v>
       </c>
       <c r="R19" t="n">
-        <v>6823410</v>
+        <v>6822684</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2537,10 +2537,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117711704</v>
+        <v>117711453</v>
       </c>
       <c r="B20" t="n">
-        <v>78218</v>
+        <v>79100</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2553,21 +2553,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>465197</v>
+        <v>465228</v>
       </c>
       <c r="R20" t="n">
-        <v>6823333</v>
+        <v>6823410</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2639,10 +2639,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117711637</v>
+        <v>117711704</v>
       </c>
       <c r="B21" t="n">
-        <v>78219</v>
+        <v>78218</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2655,21 +2655,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2679,10 +2679,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>465540</v>
+        <v>465197</v>
       </c>
       <c r="R21" t="n">
-        <v>6822684</v>
+        <v>6823333</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -4679,10 +4679,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117711689</v>
+        <v>117711986</v>
       </c>
       <c r="B41" t="n">
-        <v>78218</v>
+        <v>78127</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4695,21 +4695,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4719,10 +4719,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>465373</v>
+        <v>465243</v>
       </c>
       <c r="R41" t="n">
-        <v>6822775</v>
+        <v>6823070</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4781,10 +4781,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117711816</v>
+        <v>117711689</v>
       </c>
       <c r="B42" t="n">
-        <v>78482</v>
+        <v>78218</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4797,21 +4797,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4821,10 +4821,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>465243</v>
+        <v>465373</v>
       </c>
       <c r="R42" t="n">
-        <v>6822961</v>
+        <v>6822775</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4883,10 +4883,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117700533</v>
+        <v>117711816</v>
       </c>
       <c r="B43" t="n">
-        <v>79592</v>
+        <v>78482</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4895,38 +4895,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stygguggen, Orsa, Dlr</t>
+          <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>465554</v>
+        <v>465243</v>
       </c>
       <c r="R43" t="n">
-        <v>6822711</v>
+        <v>6822961</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4970,40 +4970,25 @@
       <c r="AG43" t="b">
         <v>0</v>
       </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117711742</v>
+        <v>117711701</v>
       </c>
       <c r="B44" t="n">
-        <v>78482</v>
+        <v>78218</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5016,21 +5001,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5040,10 +5025,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>465389</v>
+        <v>465157</v>
       </c>
       <c r="R44" t="n">
-        <v>6822818</v>
+        <v>6823202</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5102,10 +5087,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117711701</v>
+        <v>117711445</v>
       </c>
       <c r="B45" t="n">
-        <v>78218</v>
+        <v>79100</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5118,21 +5103,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5142,10 +5127,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>465157</v>
+        <v>465092</v>
       </c>
       <c r="R45" t="n">
-        <v>6823202</v>
+        <v>6823189</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5204,10 +5189,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117711445</v>
+        <v>117711745</v>
       </c>
       <c r="B46" t="n">
-        <v>79100</v>
+        <v>78482</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5220,21 +5205,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5244,10 +5229,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>465092</v>
+        <v>465507</v>
       </c>
       <c r="R46" t="n">
-        <v>6823189</v>
+        <v>6822804</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5306,10 +5291,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117711745</v>
+        <v>117711728</v>
       </c>
       <c r="B47" t="n">
-        <v>78482</v>
+        <v>90650</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5318,25 +5303,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5346,10 +5331,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>465507</v>
+        <v>465382</v>
       </c>
       <c r="R47" t="n">
-        <v>6822804</v>
+        <v>6822811</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5408,10 +5393,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117711986</v>
+        <v>117711579</v>
       </c>
       <c r="B48" t="n">
-        <v>78127</v>
+        <v>57304</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5424,34 +5409,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>353</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>465243</v>
+        <v>465419</v>
       </c>
       <c r="R48" t="n">
-        <v>6823070</v>
+        <v>6822900</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5510,10 +5503,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117711728</v>
+        <v>117700533</v>
       </c>
       <c r="B49" t="n">
-        <v>90650</v>
+        <v>79592</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5522,38 +5515,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1503</v>
+        <v>6462</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Stygguggen, Dlr</t>
+          <t>Stygguggen, Orsa, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>465382</v>
+        <v>465554</v>
       </c>
       <c r="R49" t="n">
-        <v>6822811</v>
+        <v>6822711</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5597,25 +5590,40 @@
       <c r="AG49" t="b">
         <v>0</v>
       </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117711579</v>
+        <v>117711742</v>
       </c>
       <c r="B50" t="n">
-        <v>57304</v>
+        <v>78482</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5628,42 +5636,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>465419</v>
+        <v>465389</v>
       </c>
       <c r="R50" t="n">
-        <v>6822900</v>
+        <v>6822818</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6866,10 +6866,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>117711425</v>
+        <v>117711799</v>
       </c>
       <c r="B62" t="n">
-        <v>79100</v>
+        <v>78482</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6882,21 +6882,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6906,10 +6906,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>465537</v>
+        <v>465272</v>
       </c>
       <c r="R62" t="n">
-        <v>6822683</v>
+        <v>6823356</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6968,7 +6968,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>117711426</v>
+        <v>117711425</v>
       </c>
       <c r="B63" t="n">
         <v>79100</v>
@@ -7008,10 +7008,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>465566</v>
+        <v>465537</v>
       </c>
       <c r="R63" t="n">
-        <v>6822693</v>
+        <v>6822683</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7070,10 +7070,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>117711799</v>
+        <v>117711426</v>
       </c>
       <c r="B64" t="n">
-        <v>78482</v>
+        <v>79100</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7086,21 +7086,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7110,10 +7110,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>465272</v>
+        <v>465566</v>
       </c>
       <c r="R64" t="n">
-        <v>6823356</v>
+        <v>6822693</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8600,10 +8600,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>117711630</v>
+        <v>117711449</v>
       </c>
       <c r="B79" t="n">
-        <v>78219</v>
+        <v>79100</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8616,21 +8616,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8640,10 +8640,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>465362</v>
+        <v>465140</v>
       </c>
       <c r="R79" t="n">
-        <v>6822857</v>
+        <v>6823344</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8702,10 +8702,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>117711685</v>
+        <v>117711422</v>
       </c>
       <c r="B80" t="n">
-        <v>78218</v>
+        <v>79100</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8718,41 +8718,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>465797</v>
+        <v>465425</v>
       </c>
       <c r="R80" t="n">
-        <v>6822438</v>
+        <v>6822894</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8793,7 +8786,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8812,10 +8804,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>117711443</v>
+        <v>117711400</v>
       </c>
       <c r="B81" t="n">
-        <v>79100</v>
+        <v>78516</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8828,21 +8820,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8852,10 +8844,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>465047</v>
+        <v>465326</v>
       </c>
       <c r="R81" t="n">
-        <v>6823271</v>
+        <v>6823285</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8914,10 +8906,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>117711791</v>
+        <v>117711398</v>
       </c>
       <c r="B82" t="n">
-        <v>78482</v>
+        <v>78516</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8930,21 +8922,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8954,10 +8946,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>465146</v>
+        <v>465275</v>
       </c>
       <c r="R82" t="n">
-        <v>6823190</v>
+        <v>6823367</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9016,10 +9008,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>117711449</v>
+        <v>117711685</v>
       </c>
       <c r="B83" t="n">
-        <v>79100</v>
+        <v>78218</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9032,34 +9024,41 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>465140</v>
+        <v>465797</v>
       </c>
       <c r="R83" t="n">
-        <v>6823344</v>
+        <v>6822438</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9100,6 +9099,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9118,7 +9118,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>117711422</v>
+        <v>117711443</v>
       </c>
       <c r="B84" t="n">
         <v>79100</v>
@@ -9158,10 +9158,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>465425</v>
+        <v>465047</v>
       </c>
       <c r="R84" t="n">
-        <v>6822894</v>
+        <v>6823271</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9220,10 +9220,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>117711400</v>
+        <v>117711791</v>
       </c>
       <c r="B85" t="n">
-        <v>78516</v>
+        <v>78482</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9236,21 +9236,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9260,10 +9260,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>465326</v>
+        <v>465146</v>
       </c>
       <c r="R85" t="n">
-        <v>6823285</v>
+        <v>6823190</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9322,10 +9322,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>117711398</v>
+        <v>117711630</v>
       </c>
       <c r="B86" t="n">
-        <v>78516</v>
+        <v>78219</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9338,21 +9338,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9362,10 +9362,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>465275</v>
+        <v>465362</v>
       </c>
       <c r="R86" t="n">
-        <v>6823367</v>
+        <v>6822857</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10138,10 +10138,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>117711388</v>
+        <v>117711545</v>
       </c>
       <c r="B94" t="n">
-        <v>78516</v>
+        <v>56500</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10150,38 +10150,46 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>185</v>
+        <v>100138</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>465465</v>
+        <v>465578</v>
       </c>
       <c r="R94" t="n">
-        <v>6822863</v>
+        <v>6822532</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10240,10 +10248,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>117711390</v>
+        <v>117711812</v>
       </c>
       <c r="B95" t="n">
-        <v>78516</v>
+        <v>78482</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10256,21 +10264,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10280,10 +10288,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>465508</v>
+        <v>465285</v>
       </c>
       <c r="R95" t="n">
-        <v>6822804</v>
+        <v>6823267</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10342,10 +10350,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>117711597</v>
+        <v>117711790</v>
       </c>
       <c r="B96" t="n">
-        <v>57288</v>
+        <v>78482</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10358,42 +10366,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>465248</v>
+        <v>465200</v>
       </c>
       <c r="R96" t="n">
-        <v>6823304</v>
+        <v>6823139</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10426,11 +10426,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2024-06-10</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10457,10 +10452,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>117711812</v>
+        <v>117711451</v>
       </c>
       <c r="B97" t="n">
-        <v>78482</v>
+        <v>79100</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10473,21 +10468,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10497,10 +10492,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>465285</v>
+        <v>465293</v>
       </c>
       <c r="R97" t="n">
-        <v>6823267</v>
+        <v>6823407</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10559,10 +10554,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>117711790</v>
+        <v>117711388</v>
       </c>
       <c r="B98" t="n">
-        <v>78482</v>
+        <v>78516</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10575,21 +10570,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10599,10 +10594,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>465200</v>
+        <v>465465</v>
       </c>
       <c r="R98" t="n">
-        <v>6823139</v>
+        <v>6822863</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10661,10 +10656,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>117711451</v>
+        <v>117711390</v>
       </c>
       <c r="B99" t="n">
-        <v>79100</v>
+        <v>78516</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10677,21 +10672,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10701,10 +10696,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>465293</v>
+        <v>465508</v>
       </c>
       <c r="R99" t="n">
-        <v>6823407</v>
+        <v>6822804</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10763,10 +10758,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>117711545</v>
+        <v>117711597</v>
       </c>
       <c r="B100" t="n">
-        <v>56500</v>
+        <v>57288</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10775,25 +10770,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10801,7 +10796,7 @@
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N100" t="inlineStr"/>
@@ -10811,10 +10806,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>465578</v>
+        <v>465248</v>
       </c>
       <c r="R100" t="n">
-        <v>6822532</v>
+        <v>6823304</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10847,6 +10842,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -13351,10 +13351,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>117711530</v>
+        <v>117711682</v>
       </c>
       <c r="B125" t="n">
-        <v>90501</v>
+        <v>80439</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13367,21 +13367,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1202</v>
+        <v>1049</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13391,10 +13391,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>465283</v>
+        <v>465659</v>
       </c>
       <c r="R125" t="n">
-        <v>6823280</v>
+        <v>6822514</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13453,10 +13453,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>117711682</v>
+        <v>117711530</v>
       </c>
       <c r="B126" t="n">
-        <v>80439</v>
+        <v>90501</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13469,21 +13469,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1049</v>
+        <v>1202</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13493,10 +13493,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>465659</v>
+        <v>465283</v>
       </c>
       <c r="R126" t="n">
-        <v>6822514</v>
+        <v>6823280</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>

--- a/artfynd/A 47917-2023 artfynd.xlsx
+++ b/artfynd/A 47917-2023 artfynd.xlsx
@@ -13967,7 +13967,7 @@
         <v>118734329</v>
       </c>
       <c r="B131" t="n">
-        <v>90652</v>
+        <v>90659</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14090,7 +14090,7 @@
         <v>118734327</v>
       </c>
       <c r="B132" t="n">
-        <v>91725</v>
+        <v>91732</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>

--- a/artfynd/A 47917-2023 artfynd.xlsx
+++ b/artfynd/A 47917-2023 artfynd.xlsx
@@ -13964,10 +13964,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>118734329</v>
+        <v>118734327</v>
       </c>
       <c r="B131" t="n">
-        <v>90659</v>
+        <v>91732</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -13976,25 +13976,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1235</v>
+        <v>713</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Luggskinn</t>
+          <t>Gärdselskinn</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Physodontia lundellii</t>
+          <t>Gloeodontia subasperispora</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Ryvarden &amp; H. Solheim</t>
+          <t>(Litsch.) E.Larss. &amp; K.H.Larss.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14004,10 +14004,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>465704</v>
+        <v>465375</v>
       </c>
       <c r="R131" t="n">
-        <v>6822491</v>
+        <v>6822829</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14087,10 +14087,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>118734327</v>
+        <v>118734329</v>
       </c>
       <c r="B132" t="n">
-        <v>91732</v>
+        <v>90659</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14099,25 +14099,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>713</v>
+        <v>1235</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Gärdselskinn</t>
+          <t>Luggskinn</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Gloeodontia subasperispora</t>
+          <t>Physodontia lundellii</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Litsch.) E.Larss. &amp; K.H.Larss.</t>
+          <t>Ryvarden &amp; H. Solheim</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14127,10 +14127,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>465375</v>
+        <v>465704</v>
       </c>
       <c r="R132" t="n">
-        <v>6822829</v>
+        <v>6822491</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>

--- a/artfynd/A 47917-2023 artfynd.xlsx
+++ b/artfynd/A 47917-2023 artfynd.xlsx
@@ -14210,7 +14210,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>119549076</v>
+        <v>119549081</v>
       </c>
       <c r="B133" t="n">
         <v>91840</v>
@@ -14243,26 +14243,17 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>465493</v>
+        <v>465117</v>
       </c>
       <c r="R133" t="n">
-        <v>6822703</v>
+        <v>6823172</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14321,10 +14312,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>119549073</v>
+        <v>119549079</v>
       </c>
       <c r="B134" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14333,38 +14324,47 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>465556</v>
+        <v>465286</v>
       </c>
       <c r="R134" t="n">
-        <v>6822565</v>
+        <v>6823382</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14423,7 +14423,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>119549079</v>
+        <v>119549077</v>
       </c>
       <c r="B135" t="n">
         <v>91840</v>
@@ -14458,7 +14458,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -14472,10 +14472,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>465286</v>
+        <v>465527</v>
       </c>
       <c r="R135" t="n">
-        <v>6823382</v>
+        <v>6822634</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14534,10 +14534,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>119549082</v>
+        <v>119549073</v>
       </c>
       <c r="B136" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14546,25 +14546,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14574,10 +14574,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>465128</v>
+        <v>465556</v>
       </c>
       <c r="R136" t="n">
-        <v>6823166</v>
+        <v>6822565</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14636,7 +14636,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>119549077</v>
+        <v>119549082</v>
       </c>
       <c r="B137" t="n">
         <v>91840</v>
@@ -14669,26 +14669,17 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>465527</v>
+        <v>465128</v>
       </c>
       <c r="R137" t="n">
-        <v>6822634</v>
+        <v>6823166</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14747,7 +14738,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>119549081</v>
+        <v>119549076</v>
       </c>
       <c r="B138" t="n">
         <v>91840</v>
@@ -14780,17 +14771,26 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I138" t="inlineStr"/>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>465117</v>
+        <v>465493</v>
       </c>
       <c r="R138" t="n">
-        <v>6823172</v>
+        <v>6822703</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>

--- a/artfynd/A 47917-2023 artfynd.xlsx
+++ b/artfynd/A 47917-2023 artfynd.xlsx
@@ -14210,7 +14210,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>119549081</v>
+        <v>119549079</v>
       </c>
       <c r="B133" t="n">
         <v>91840</v>
@@ -14243,17 +14243,26 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr"/>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>465117</v>
+        <v>465286</v>
       </c>
       <c r="R133" t="n">
-        <v>6823172</v>
+        <v>6823382</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14312,10 +14321,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>119549079</v>
+        <v>119549073</v>
       </c>
       <c r="B134" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14324,47 +14333,38 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>465286</v>
+        <v>465556</v>
       </c>
       <c r="R134" t="n">
-        <v>6823382</v>
+        <v>6822565</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14534,10 +14534,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>119549073</v>
+        <v>119549076</v>
       </c>
       <c r="B136" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14546,38 +14546,47 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>465556</v>
+        <v>465493</v>
       </c>
       <c r="R136" t="n">
-        <v>6822565</v>
+        <v>6822703</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14738,7 +14747,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>119549076</v>
+        <v>119549081</v>
       </c>
       <c r="B138" t="n">
         <v>91840</v>
@@ -14771,26 +14780,17 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>465493</v>
+        <v>465117</v>
       </c>
       <c r="R138" t="n">
-        <v>6822703</v>
+        <v>6823172</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>

--- a/artfynd/A 47917-2023 artfynd.xlsx
+++ b/artfynd/A 47917-2023 artfynd.xlsx
@@ -4052,7 +4052,7 @@
         <v>117711592</v>
       </c>
       <c r="B35" t="n">
-        <v>57290</v>
+        <v>57478</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>117711536</v>
       </c>
       <c r="B52" t="n">
-        <v>57290</v>
+        <v>57478</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -8897,7 +8897,7 @@
         <v>117711602</v>
       </c>
       <c r="B82" t="n">
-        <v>57290</v>
+        <v>57478</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10040,7 +10040,7 @@
         <v>117711597</v>
       </c>
       <c r="B93" t="n">
-        <v>57290</v>
+        <v>57478</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -12714,7 +12714,7 @@
         <v>117711535</v>
       </c>
       <c r="B119" t="n">
-        <v>57290</v>
+        <v>57478</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>

--- a/artfynd/A 47917-2023 artfynd.xlsx
+++ b/artfynd/A 47917-2023 artfynd.xlsx
@@ -4052,7 +4052,7 @@
         <v>117711592</v>
       </c>
       <c r="B35" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>117711536</v>
       </c>
       <c r="B52" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -8897,7 +8897,7 @@
         <v>117711602</v>
       </c>
       <c r="B82" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10040,7 +10040,7 @@
         <v>117711597</v>
       </c>
       <c r="B93" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -12714,7 +12714,7 @@
         <v>117711535</v>
       </c>
       <c r="B119" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
